--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,6727 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131888264</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497993</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7040023</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131888312</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>498192</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7040124</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om garnlav på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131888283</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97903</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498177</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7040311</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131888266</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498035</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7040010</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131888314</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498244</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7040234</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131888262</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497936</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7040038</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131888258</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498240</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7040291</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131889555</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>498078</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7040055</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131889570</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83110</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>498129</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7040319</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131888294</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>498217</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7040172</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131888272</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>498063</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7040346</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131889553</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497949</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040132</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131888270</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>498183</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7040110</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, enstaka några meter upp på en gran.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131888310</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>498071</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7040023</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131888309</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>498001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7040034</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på flera granar här.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131888313</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>498228</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7040198</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med garnlavsbålar på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131889562</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>498066</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7040263</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131889546</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>498059</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7040135</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131889547</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>498049</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7040051</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131888265</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>498010</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7040021</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131888296</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>498076</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7040326</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131889564</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>498048</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7040043</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131888317</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>498063</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7040322</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131888288</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80405</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>498246</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7040207</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Naturskog dominerad av gran med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131888257</v>
+      </c>
+      <c r="B27" t="n">
+        <v>83244</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>498300</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7040266</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131889569</v>
+      </c>
+      <c r="B28" t="n">
+        <v>83110</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>498205</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7040233</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131888269</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>498161</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7040066</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131888263</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>497963</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7040031</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131889558</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>498144</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7040300</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131888308</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>497942</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7040052</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131888318</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>498079</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7040353</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Garnlav på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131888268</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>498140</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7040032</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131889548</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>498083</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7040302</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131888261</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>497929</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7040047</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131888287</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80369</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>498148</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7040325</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131889554</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>498048</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7040052</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131888271</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>498306</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7040264</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131889556</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>498308</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7040314</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131888316</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>498131</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7040328</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131888286</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80369</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>498252</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7040210</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131888279</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>498136</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7040344</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131888295</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>498147</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7040335</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131888315</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>498187</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7040294</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131888311</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>498126</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7040057</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131889541</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78276</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>498162</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7040231</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131889535</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>497945</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7040123</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131889544</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78276</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>498103</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7040280</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131889537</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>498206</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7040254</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131889538</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>498308</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7040314</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131889536</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>498140</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7040150</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131889529</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>498137</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7040255</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131889539</v>
+      </c>
+      <c r="B54" t="n">
+        <v>83235</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>492</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>498080</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7040050</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Naturskog med påtagligt höga naturvärden.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888265</v>
+        <v>131889564</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,31 +3233,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3265,10 +3260,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498010</v>
+        <v>498048</v>
       </c>
       <c r="R22" t="n">
-        <v>7040021</v>
+        <v>7040043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3305,7 +3300,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3314,6 +3309,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3322,6 +3318,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3332,9 +3333,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3352,10 +3358,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131888296</v>
+        <v>131888265</v>
       </c>
       <c r="B23" t="n">
-        <v>91828</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,28 +3369,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3394,10 +3401,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498076</v>
+        <v>498010</v>
       </c>
       <c r="R23" t="n">
-        <v>7040326</v>
+        <v>7040021</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3434,7 +3441,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3443,7 +3450,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3482,10 +3488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131889564</v>
+        <v>131888296</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>91828</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3493,26 +3499,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3520,10 +3530,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498048</v>
+        <v>498076</v>
       </c>
       <c r="R24" t="n">
-        <v>7040043</v>
+        <v>7040326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3560,7 +3570,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3578,11 +3588,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3593,14 +3598,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131888269</v>
+        <v>131889558</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4157,29 +4157,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4189,10 +4184,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498161</v>
+        <v>498144</v>
       </c>
       <c r="R29" t="n">
-        <v>7040066</v>
+        <v>7040300</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4227,17 +4222,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4246,6 +4237,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4256,14 +4252,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4281,7 +4272,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888263</v>
+        <v>131888269</v>
       </c>
       <c r="B30" t="n">
         <v>57902</v>
@@ -4324,10 +4315,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497963</v>
+        <v>498161</v>
       </c>
       <c r="R30" t="n">
-        <v>7040031</v>
+        <v>7040066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4364,7 +4355,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4391,9 +4382,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4411,10 +4407,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131889558</v>
+        <v>131888263</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,24 +4418,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4449,10 +4450,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498144</v>
+        <v>497963</v>
       </c>
       <c r="R31" t="n">
-        <v>7040300</v>
+        <v>7040031</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4487,24 +4488,23 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -6464,10 +6464,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131889541</v>
+        <v>131889803</v>
       </c>
       <c r="B47" t="n">
-        <v>78276</v>
+        <v>57902</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6475,26 +6475,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>498162</v>
+        <v>498061</v>
       </c>
       <c r="R47" t="n">
-        <v>7040231</v>
+        <v>7040333</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6540,13 +6545,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6557,7 +6566,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6570,9 +6579,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6590,7 +6604,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131889535</v>
+        <v>131889798</v>
       </c>
       <c r="B48" t="n">
         <v>57902</v>
@@ -6633,10 +6647,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497945</v>
+        <v>498109</v>
       </c>
       <c r="R48" t="n">
-        <v>7040123</v>
+        <v>7040366</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6730,10 +6744,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889544</v>
+        <v>131889782</v>
       </c>
       <c r="B49" t="n">
-        <v>78276</v>
+        <v>91832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6741,26 +6755,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6768,10 +6786,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498103</v>
+        <v>498206</v>
       </c>
       <c r="R49" t="n">
-        <v>7040280</v>
+        <v>7040320</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6823,7 +6841,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6856,10 +6874,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131889537</v>
+        <v>131889541</v>
       </c>
       <c r="B50" t="n">
-        <v>57902</v>
+        <v>78276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6867,31 +6885,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6899,10 +6912,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>498206</v>
+        <v>498162</v>
       </c>
       <c r="R50" t="n">
-        <v>7040254</v>
+        <v>7040231</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6937,17 +6950,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6958,7 +6967,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6971,14 +6980,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6996,10 +7000,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131889538</v>
+        <v>131889535</v>
       </c>
       <c r="B51" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7007,16 +7011,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7039,10 +7043,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>498308</v>
+        <v>497945</v>
       </c>
       <c r="R51" t="n">
-        <v>7040314</v>
+        <v>7040123</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska hackspår.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7096,6 +7100,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ51" t="inlineStr">
         <is>
           <t>gran</t>
@@ -7106,9 +7115,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7126,10 +7140,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889536</v>
+        <v>131889854</v>
       </c>
       <c r="B52" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7137,29 +7151,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7169,10 +7178,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>498140</v>
+        <v>498128</v>
       </c>
       <c r="R52" t="n">
-        <v>7040150</v>
+        <v>7040149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7207,17 +7216,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7261,7 +7266,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889529</v>
+        <v>131889781</v>
       </c>
       <c r="B53" t="n">
         <v>91832</v>
@@ -7303,10 +7308,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>498137</v>
+        <v>498266</v>
       </c>
       <c r="R53" t="n">
-        <v>7040255</v>
+        <v>7040341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7391,37 +7396,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889539</v>
+        <v>131889830</v>
       </c>
       <c r="B54" t="n">
-        <v>83235</v>
+        <v>91828</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7429,10 +7438,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>498080</v>
+        <v>498191</v>
       </c>
       <c r="R54" t="n">
-        <v>7040050</v>
+        <v>7040363</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7482,11 +7491,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Naturskog med påtagligt höga naturvärden.</t>
-        </is>
-      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
@@ -7499,6 +7503,4555 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131889826</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92131</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>658</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>498076</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7040234</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131889822</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>498186</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7040355</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131889801</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>498071</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7040353</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131889544</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78276</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>498103</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7040280</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131889842</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>498010</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7040140</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131889824</v>
+      </c>
+      <c r="B60" t="n">
+        <v>83235</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>492</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>498306</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7040323</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131889793</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92555</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>498094</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7040104</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131889861</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>498269</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7040359</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131889792</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92555</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>498107</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7040204</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131889862</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>498155</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7040384</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131889879</v>
+      </c>
+      <c r="B65" t="n">
+        <v>89217</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>510</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>498139</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7040231</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131889780</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>498200</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7040160</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131889537</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>498206</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7040254</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131889858</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>498181</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7040135</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Särskilt rikligt med garnlav här!</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131889846</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>498217</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7040214</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131889837</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>498184</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7040321</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131889538</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>498308</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7040314</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131889536</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>498140</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7040150</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131889794</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92555</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>498247</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7040357</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131889860</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>498192</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7040190</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131889843</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>498151</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7040238</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131889799</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>498091</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7040360</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131889825</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>498076</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7040226</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131889841</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92206</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>498085</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7040081</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131889833</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>498237</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7040342</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131889800</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>498089</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7040360</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131889788</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>498075</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7040043</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131889787</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>498084</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7040232</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131889844</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>498077</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7040086</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131889857</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>498028</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7040149</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131889779</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>498070</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7040031</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131889845</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>498096</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7040105</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131889529</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>498137</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7040255</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>131889539</v>
+      </c>
+      <c r="B88" t="n">
+        <v>83235</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>492</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>498080</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7040050</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Naturskog med påtagligt höga naturvärden.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131889877</v>
+      </c>
+      <c r="B89" t="n">
+        <v>83110</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>498149</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7040159</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131888264</v>
+        <v>131888312</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,31 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497993</v>
+        <v>498192</v>
       </c>
       <c r="R3" t="n">
-        <v>7040023</v>
+        <v>7040124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +859,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,12 +889,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131888312</v>
+        <v>131888264</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,26 +923,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498192</v>
+        <v>497993</v>
       </c>
       <c r="R4" t="n">
-        <v>7040124</v>
+        <v>7040023</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1004,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
         <v>131888283</v>
       </c>
       <c r="B5" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131888266</v>
+        <v>131888314</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,31 +1165,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1197,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498035</v>
+        <v>498244</v>
       </c>
       <c r="R6" t="n">
-        <v>7040010</v>
+        <v>7040234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,6 +1241,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888314</v>
+        <v>131888266</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,26 +1291,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498244</v>
+        <v>498035</v>
       </c>
       <c r="R7" t="n">
-        <v>7040234</v>
+        <v>7040010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,7 +1363,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1372,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1410,40 +1410,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888262</v>
+        <v>131888258</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1453,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497936</v>
+        <v>498240</v>
       </c>
       <c r="R8" t="n">
-        <v>7040038</v>
+        <v>7040291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,17 +1490,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1520,9 +1515,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1540,34 +1540,30 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888258</v>
+        <v>131889555</v>
       </c>
       <c r="B9" t="n">
-        <v>91795</v>
+        <v>91858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -1582,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498240</v>
+        <v>498078</v>
       </c>
       <c r="R9" t="n">
-        <v>7040291</v>
+        <v>7040055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,14 +1641,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1670,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131889555</v>
+        <v>131888262</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,24 +1672,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1708,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498078</v>
+        <v>497936</v>
       </c>
       <c r="R10" t="n">
-        <v>7040055</v>
+        <v>7040038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,13 +1742,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>131889570</v>
       </c>
       <c r="B11" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888294</v>
+        <v>131888272</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,28 +1933,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1964,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498217</v>
+        <v>498063</v>
       </c>
       <c r="R12" t="n">
-        <v>7040172</v>
+        <v>7040346</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2004,7 +2005,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,7 +2014,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888272</v>
+        <v>131888294</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>91834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,29 +2068,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2100,10 +2099,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498063</v>
+        <v>498217</v>
       </c>
       <c r="R13" t="n">
-        <v>7040346</v>
+        <v>7040172</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2139,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,6 +2148,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2169,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
         <v>131889553</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131888270</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131888310</v>
+        <v>131889546</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,26 +2459,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2486,10 +2490,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498071</v>
+        <v>498059</v>
       </c>
       <c r="R16" t="n">
-        <v>7040023</v>
+        <v>7040135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2524,11 +2528,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2542,6 +2541,11 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2577,7 +2581,7 @@
         <v>131888309</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,10 +2709,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131888313</v>
+        <v>131889562</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2743,10 +2747,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498228</v>
+        <v>498066</v>
       </c>
       <c r="R18" t="n">
-        <v>7040198</v>
+        <v>7040263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med garnlavsbålar på flera granar.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,6 +2805,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2811,9 +2820,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2831,10 +2845,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131889562</v>
+        <v>131888310</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2869,10 +2883,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498066</v>
+        <v>498071</v>
       </c>
       <c r="R19" t="n">
-        <v>7040263</v>
+        <v>7040023</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2909,7 +2923,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2927,11 +2941,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2942,14 +2951,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2967,10 +2971,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131889546</v>
+        <v>131888313</v>
       </c>
       <c r="B20" t="n">
-        <v>91828</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2978,30 +2982,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498059</v>
+        <v>498228</v>
       </c>
       <c r="R20" t="n">
-        <v>7040135</v>
+        <v>7040198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,6 +3047,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med garnlavsbålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3060,11 +3065,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3100,7 +3100,7 @@
         <v>131889547</v>
       </c>
       <c r="B21" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131889564</v>
+        <v>131888296</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,26 +3233,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3260,10 +3264,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498048</v>
+        <v>498076</v>
       </c>
       <c r="R22" t="n">
-        <v>7040043</v>
+        <v>7040326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3300,7 +3304,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3318,11 +3322,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3333,14 +3332,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3358,10 +3352,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131888265</v>
+        <v>131889564</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3369,31 +3363,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3401,10 +3390,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498010</v>
+        <v>498048</v>
       </c>
       <c r="R23" t="n">
-        <v>7040021</v>
+        <v>7040043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3441,7 +3430,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3450,6 +3439,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3458,6 +3448,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3468,9 +3463,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888296</v>
+        <v>131888265</v>
       </c>
       <c r="B24" t="n">
-        <v>91828</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,28 +3499,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3530,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498076</v>
+        <v>498010</v>
       </c>
       <c r="R24" t="n">
-        <v>7040326</v>
+        <v>7040021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3570,7 +3571,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3579,7 +3580,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>131888317</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>131888288</v>
       </c>
       <c r="B26" t="n">
-        <v>80405</v>
+        <v>80407</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>131888257</v>
       </c>
       <c r="B27" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>131889569</v>
       </c>
       <c r="B28" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>131889558</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888269</v>
+        <v>131888263</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498161</v>
+        <v>497963</v>
       </c>
       <c r="R30" t="n">
-        <v>7040066</v>
+        <v>7040031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4382,14 +4382,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4407,10 +4402,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888263</v>
+        <v>131888269</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4450,10 +4445,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497963</v>
+        <v>498161</v>
       </c>
       <c r="R31" t="n">
-        <v>7040031</v>
+        <v>7040066</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4517,9 +4512,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131888308</v>
+        <v>131888268</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,26 +4548,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4575,10 +4580,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497942</v>
+        <v>498140</v>
       </c>
       <c r="R32" t="n">
-        <v>7040052</v>
+        <v>7040032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4615,7 +4620,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4624,7 +4629,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4643,9 +4647,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4663,10 +4672,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888318</v>
+        <v>131889548</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>91834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4674,26 +4683,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4701,10 +4714,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498079</v>
+        <v>498083</v>
       </c>
       <c r="R33" t="n">
-        <v>7040353</v>
+        <v>7040302</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4737,11 +4750,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4789,10 +4797,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888268</v>
+        <v>131888318</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4800,31 +4808,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4832,10 +4835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498140</v>
+        <v>498079</v>
       </c>
       <c r="R34" t="n">
-        <v>7040032</v>
+        <v>7040353</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4872,7 +4875,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4881,6 +4884,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4899,14 +4903,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4924,10 +4923,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131889548</v>
+        <v>131888308</v>
       </c>
       <c r="B35" t="n">
-        <v>91828</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4935,30 +4934,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4966,10 +4961,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498083</v>
+        <v>497942</v>
       </c>
       <c r="R35" t="n">
-        <v>7040302</v>
+        <v>7040052</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5002,6 +4997,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131888261</v>
+        <v>131888287</v>
       </c>
       <c r="B36" t="n">
-        <v>57902</v>
+        <v>80371</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5060,29 +5060,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5092,10 +5091,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497929</v>
+        <v>498148</v>
       </c>
       <c r="R36" t="n">
-        <v>7040047</v>
+        <v>7040325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5132,7 +5131,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5141,6 +5140,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5151,22 +5151,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131888287</v>
+        <v>131889554</v>
       </c>
       <c r="B37" t="n">
-        <v>80369</v>
+        <v>91858</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5195,28 +5195,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5226,10 +5222,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>498148</v>
+        <v>498048</v>
       </c>
       <c r="R37" t="n">
-        <v>7040325</v>
+        <v>7040052</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5264,11 +5260,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5286,22 +5277,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5319,10 +5305,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131889554</v>
+        <v>131888261</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5330,24 +5316,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5357,10 +5348,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>498048</v>
+        <v>497929</v>
       </c>
       <c r="R38" t="n">
-        <v>7040052</v>
+        <v>7040047</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5395,13 +5386,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5420,9 +5415,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131888271</v>
+        <v>131889556</v>
       </c>
       <c r="B39" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5451,29 +5451,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>498306</v>
+        <v>498308</v>
       </c>
       <c r="R39" t="n">
-        <v>7040264</v>
+        <v>7040314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5521,17 +5516,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5550,14 +5541,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5575,10 +5561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131889556</v>
+        <v>131888271</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5586,24 +5572,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5613,10 +5604,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>498308</v>
+        <v>498306</v>
       </c>
       <c r="R40" t="n">
-        <v>7040314</v>
+        <v>7040264</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5651,13 +5642,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5676,9 +5671,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
         <v>131888316</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>131888286</v>
       </c>
       <c r="B42" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5957,40 +5957,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888279</v>
+        <v>131888295</v>
       </c>
       <c r="B43" t="n">
-        <v>57090</v>
+        <v>91834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6000,10 +5999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498136</v>
+        <v>498147</v>
       </c>
       <c r="R43" t="n">
-        <v>7040344</v>
+        <v>7040335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6040,7 +6039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6049,12 +6048,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6072,39 +6092,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888295</v>
+        <v>131888279</v>
       </c>
       <c r="B44" t="n">
-        <v>91828</v>
+        <v>57092</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6114,10 +6135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498147</v>
+        <v>498136</v>
       </c>
       <c r="R44" t="n">
-        <v>7040335</v>
+        <v>7040344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6154,7 +6175,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6163,33 +6184,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
         <v>131888315</v>
       </c>
       <c r="B45" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>131888311</v>
       </c>
       <c r="B46" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131889803</v>
+        <v>131889782</v>
       </c>
       <c r="B47" t="n">
-        <v>57902</v>
+        <v>91838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6475,29 +6475,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6507,10 +6506,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>498061</v>
+        <v>498206</v>
       </c>
       <c r="R47" t="n">
-        <v>7040333</v>
+        <v>7040320</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6545,17 +6544,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6579,14 +6574,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6604,10 +6594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131889798</v>
+        <v>131889803</v>
       </c>
       <c r="B48" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6647,10 +6637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>498109</v>
+        <v>498061</v>
       </c>
       <c r="R48" t="n">
-        <v>7040366</v>
+        <v>7040333</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,10 +6734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889782</v>
+        <v>131889798</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6755,28 +6745,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6786,10 +6777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498206</v>
+        <v>498109</v>
       </c>
       <c r="R49" t="n">
-        <v>7040320</v>
+        <v>7040366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6824,13 +6815,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6854,9 +6849,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6877,7 +6877,7 @@
         <v>131889541</v>
       </c>
       <c r="B50" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131889535</v>
+        <v>131889854</v>
       </c>
       <c r="B51" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7011,29 +7011,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7043,10 +7038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497945</v>
+        <v>498128</v>
       </c>
       <c r="R51" t="n">
-        <v>7040123</v>
+        <v>7040149</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7081,17 +7076,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7115,14 +7106,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7140,10 +7126,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889854</v>
+        <v>131889535</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7151,24 +7137,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7178,10 +7169,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>498128</v>
+        <v>497945</v>
       </c>
       <c r="R52" t="n">
-        <v>7040149</v>
+        <v>7040123</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7216,13 +7207,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7246,9 +7241,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889781</v>
+        <v>131889830</v>
       </c>
       <c r="B53" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7277,21 +7277,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>498266</v>
+        <v>498191</v>
       </c>
       <c r="R53" t="n">
-        <v>7040341</v>
+        <v>7040363</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7359,26 +7359,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7396,10 +7376,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889830</v>
+        <v>131889781</v>
       </c>
       <c r="B54" t="n">
-        <v>91828</v>
+        <v>91838</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7407,21 +7387,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7438,10 +7418,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>498191</v>
+        <v>498266</v>
       </c>
       <c r="R54" t="n">
-        <v>7040363</v>
+        <v>7040341</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7489,6 +7469,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7509,7 +7509,7 @@
         <v>131889826</v>
       </c>
       <c r="B55" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>131889822</v>
       </c>
       <c r="B56" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>131889801</v>
       </c>
       <c r="B57" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>131889544</v>
       </c>
       <c r="B58" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8034,37 +8034,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889842</v>
+        <v>131889824</v>
       </c>
       <c r="B59" t="n">
-        <v>91852</v>
+        <v>83237</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498010</v>
+        <v>498306</v>
       </c>
       <c r="R59" t="n">
-        <v>7040140</v>
+        <v>7040323</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8128,21 +8128,6 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8160,37 +8145,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889824</v>
+        <v>131889842</v>
       </c>
       <c r="B60" t="n">
-        <v>83235</v>
+        <v>91858</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8198,10 +8183,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498306</v>
+        <v>498010</v>
       </c>
       <c r="R60" t="n">
-        <v>7040323</v>
+        <v>7040140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8254,6 +8239,21 @@
       <c r="AI60" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8271,41 +8271,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889793</v>
+        <v>131889861</v>
       </c>
       <c r="B61" t="n">
-        <v>92555</v>
+        <v>79266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8313,10 +8309,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>498094</v>
+        <v>498269</v>
       </c>
       <c r="R61" t="n">
-        <v>7040104</v>
+        <v>7040359</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8351,6 +8347,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8381,9 +8382,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8401,37 +8407,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889861</v>
+        <v>131889793</v>
       </c>
       <c r="B62" t="n">
-        <v>79264</v>
+        <v>92561</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8439,10 +8449,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>498269</v>
+        <v>498094</v>
       </c>
       <c r="R62" t="n">
-        <v>7040359</v>
+        <v>7040104</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8477,11 +8487,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8512,14 +8517,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8540,7 +8540,7 @@
         <v>131889792</v>
       </c>
       <c r="B63" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8667,10 +8667,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889862</v>
+        <v>131889879</v>
       </c>
       <c r="B64" t="n">
-        <v>79264</v>
+        <v>89223</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8678,26 +8678,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8705,10 +8709,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>498155</v>
+        <v>498139</v>
       </c>
       <c r="R64" t="n">
-        <v>7040384</v>
+        <v>7040231</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8743,11 +8747,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8778,9 +8777,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8798,10 +8802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889879</v>
+        <v>131889862</v>
       </c>
       <c r="B65" t="n">
-        <v>89217</v>
+        <v>79266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8809,30 +8813,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>498139</v>
+        <v>498155</v>
       </c>
       <c r="R65" t="n">
-        <v>7040231</v>
+        <v>7040384</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8878,6 +8878,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8908,14 +8913,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8936,7 +8936,7 @@
         <v>131889780</v>
       </c>
       <c r="B66" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889537</v>
+        <v>131889846</v>
       </c>
       <c r="B67" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,29 +9074,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498206</v>
+        <v>498217</v>
       </c>
       <c r="R67" t="n">
-        <v>7040254</v>
+        <v>7040214</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9144,17 +9139,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9163,11 +9154,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9178,14 +9164,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9206,7 +9187,7 @@
         <v>131889858</v>
       </c>
       <c r="B68" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9342,10 +9323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889846</v>
+        <v>131889537</v>
       </c>
       <c r="B69" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9353,24 +9334,29 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9380,10 +9366,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498217</v>
+        <v>498206</v>
       </c>
       <c r="R69" t="n">
-        <v>7040214</v>
+        <v>7040254</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9418,13 +9404,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9433,6 +9423,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ69" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9443,9 +9438,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
         <v>131889837</v>
       </c>
       <c r="B70" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>131889538</v>
       </c>
       <c r="B71" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9723,10 +9723,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889536</v>
+        <v>131889860</v>
       </c>
       <c r="B72" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9734,31 +9734,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9766,10 +9761,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>498140</v>
+        <v>498192</v>
       </c>
       <c r="R72" t="n">
-        <v>7040150</v>
+        <v>7040190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9806,7 +9801,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9815,17 +9810,13 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9861,7 +9852,7 @@
         <v>131889794</v>
       </c>
       <c r="B73" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9988,10 +9979,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889860</v>
+        <v>131889536</v>
       </c>
       <c r="B74" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9999,26 +9990,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10026,10 +10022,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498192</v>
+        <v>498140</v>
       </c>
       <c r="R74" t="n">
-        <v>7040190</v>
+        <v>7040150</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10066,7 +10062,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10075,13 +10071,17 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10117,7 +10117,7 @@
         <v>131889843</v>
       </c>
       <c r="B75" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>131889799</v>
       </c>
       <c r="B76" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>131889825</v>
       </c>
       <c r="B77" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889841</v>
+        <v>131889833</v>
       </c>
       <c r="B78" t="n">
-        <v>92206</v>
+        <v>91834</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498085</v>
+        <v>498237</v>
       </c>
       <c r="R78" t="n">
-        <v>7040081</v>
+        <v>7040342</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10607,22 +10607,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10640,10 +10635,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889833</v>
+        <v>131889788</v>
       </c>
       <c r="B79" t="n">
-        <v>91828</v>
+        <v>91838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10651,21 +10646,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10682,10 +10677,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>498237</v>
+        <v>498075</v>
       </c>
       <c r="R79" t="n">
-        <v>7040342</v>
+        <v>7040043</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10770,40 +10765,39 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131889800</v>
+        <v>131889841</v>
       </c>
       <c r="B80" t="n">
-        <v>57902</v>
+        <v>92212</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -10813,10 +10807,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>498089</v>
+        <v>498085</v>
       </c>
       <c r="R80" t="n">
-        <v>7040360</v>
+        <v>7040081</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10851,17 +10845,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10877,22 +10867,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10910,10 +10900,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131889788</v>
+        <v>131889800</v>
       </c>
       <c r="B81" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10921,28 +10911,29 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10952,10 +10943,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498075</v>
+        <v>498089</v>
       </c>
       <c r="R81" t="n">
-        <v>7040043</v>
+        <v>7040360</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10990,13 +10981,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11020,9 +11015,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11043,7 +11043,7 @@
         <v>131889787</v>
       </c>
       <c r="B82" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11170,10 +11170,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131889844</v>
+        <v>131889857</v>
       </c>
       <c r="B83" t="n">
-        <v>91852</v>
+        <v>79266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11181,26 +11181,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11208,10 +11208,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>498077</v>
+        <v>498028</v>
       </c>
       <c r="R83" t="n">
-        <v>7040086</v>
+        <v>7040149</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11244,6 +11244,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11296,10 +11301,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131889857</v>
+        <v>131889844</v>
       </c>
       <c r="B84" t="n">
-        <v>79264</v>
+        <v>91858</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11307,26 +11312,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11334,10 +11339,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>498028</v>
+        <v>498077</v>
       </c>
       <c r="R84" t="n">
-        <v>7040149</v>
+        <v>7040086</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11370,11 +11375,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11430,7 +11430,7 @@
         <v>131889779</v>
       </c>
       <c r="B85" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11562,37 +11562,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889845</v>
+        <v>131889539</v>
       </c>
       <c r="B86" t="n">
-        <v>91852</v>
+        <v>83237</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11600,10 +11600,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498096</v>
+        <v>498080</v>
       </c>
       <c r="R86" t="n">
-        <v>7040105</v>
+        <v>7040050</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11655,22 +11655,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Naturskog med påtagligt höga naturvärden.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11691,7 +11676,7 @@
         <v>131889529</v>
       </c>
       <c r="B87" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11818,37 +11803,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889539</v>
+        <v>131889845</v>
       </c>
       <c r="B88" t="n">
-        <v>83235</v>
+        <v>91858</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11856,10 +11841,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>498080</v>
+        <v>498096</v>
       </c>
       <c r="R88" t="n">
-        <v>7040050</v>
+        <v>7040105</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11911,7 +11896,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Naturskog med påtagligt höga naturvärden.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11932,7 +11932,7 @@
         <v>131889877</v>
       </c>
       <c r="B89" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131888312</v>
+        <v>131888264</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,26 +792,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498192</v>
+        <v>497993</v>
       </c>
       <c r="R3" t="n">
-        <v>7040124</v>
+        <v>7040023</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,7 +864,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,12 +893,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131888264</v>
+        <v>131888312</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,31 +927,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497993</v>
+        <v>498192</v>
       </c>
       <c r="R4" t="n">
-        <v>7040023</v>
+        <v>7040124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +1003,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,38 +1047,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888283</v>
+        <v>131888266</v>
       </c>
       <c r="B5" t="n">
-        <v>97909</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498177</v>
+        <v>498035</v>
       </c>
       <c r="R5" t="n">
-        <v>7040311</v>
+        <v>7040010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,19 +1128,38 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1280,42 +1303,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888266</v>
+        <v>131888283</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>97909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,10 +1342,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498035</v>
+        <v>498177</v>
       </c>
       <c r="R7" t="n">
-        <v>7040010</v>
+        <v>7040311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,38 +1380,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888296</v>
+        <v>131888265</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,28 +3233,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3264,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498076</v>
+        <v>498010</v>
       </c>
       <c r="R22" t="n">
-        <v>7040326</v>
+        <v>7040021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3304,7 +3305,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,7 +3314,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131889564</v>
+        <v>131888296</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>91834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,26 +3363,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3390,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498048</v>
+        <v>498076</v>
       </c>
       <c r="R23" t="n">
-        <v>7040043</v>
+        <v>7040326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3430,7 +3434,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3448,11 +3452,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3463,14 +3462,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3488,10 +3482,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888265</v>
+        <v>131889564</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,31 +3493,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3531,10 +3520,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498010</v>
+        <v>498048</v>
       </c>
       <c r="R24" t="n">
-        <v>7040021</v>
+        <v>7040043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3571,7 +3560,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3580,6 +3569,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3588,6 +3578,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3598,9 +3593,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B27" t="n">
-        <v>83246</v>
+        <v>83112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R27" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,11 +3960,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3995,14 +3990,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4020,10 +4010,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B28" t="n">
-        <v>83112</v>
+        <v>83246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4031,21 +4021,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4058,10 +4048,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R28" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4096,6 +4086,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4126,9 +4121,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131889558</v>
+        <v>131888263</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4157,24 +4157,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4184,10 +4189,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498144</v>
+        <v>497963</v>
       </c>
       <c r="R29" t="n">
-        <v>7040300</v>
+        <v>7040031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4222,24 +4227,23 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4272,7 +4276,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888263</v>
+        <v>131888269</v>
       </c>
       <c r="B30" t="n">
         <v>57904</v>
@@ -4315,10 +4319,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497963</v>
+        <v>498161</v>
       </c>
       <c r="R30" t="n">
-        <v>7040031</v>
+        <v>7040066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4355,7 +4359,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4382,9 +4386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4402,10 +4411,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888269</v>
+        <v>131889558</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4413,29 +4422,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4445,10 +4449,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498161</v>
+        <v>498144</v>
       </c>
       <c r="R31" t="n">
-        <v>7040066</v>
+        <v>7040300</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4483,17 +4487,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4502,6 +4502,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4512,14 +4517,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131888268</v>
+        <v>131889548</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,29 +4548,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4580,10 +4579,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498140</v>
+        <v>498083</v>
       </c>
       <c r="R32" t="n">
-        <v>7040032</v>
+        <v>7040302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4618,17 +4617,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4647,14 +4642,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4672,10 +4662,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131889548</v>
+        <v>131888318</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4683,30 +4673,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4714,10 +4700,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498083</v>
+        <v>498079</v>
       </c>
       <c r="R33" t="n">
-        <v>7040302</v>
+        <v>7040353</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4750,6 +4736,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4797,7 +4788,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888318</v>
+        <v>131888308</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4835,10 +4826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498079</v>
+        <v>497942</v>
       </c>
       <c r="R34" t="n">
-        <v>7040353</v>
+        <v>7040052</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4875,7 +4866,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4923,10 +4914,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888308</v>
+        <v>131888268</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4934,26 +4925,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4961,10 +4957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497942</v>
+        <v>498140</v>
       </c>
       <c r="R35" t="n">
-        <v>7040052</v>
+        <v>7040032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5001,7 +4997,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5010,7 +5006,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5029,9 +5024,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888286</v>
+        <v>131888295</v>
       </c>
       <c r="B42" t="n">
-        <v>80371</v>
+        <v>91834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498252</v>
+        <v>498147</v>
       </c>
       <c r="R42" t="n">
-        <v>7040210</v>
+        <v>7040335</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,39 +5957,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888295</v>
+        <v>131888279</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>57092</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5999,10 +6000,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498147</v>
+        <v>498136</v>
       </c>
       <c r="R43" t="n">
-        <v>7040335</v>
+        <v>7040344</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6039,7 +6040,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6048,33 +6049,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6092,40 +6072,39 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888279</v>
+        <v>131888286</v>
       </c>
       <c r="B44" t="n">
-        <v>57092</v>
+        <v>80371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6135,10 +6114,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498136</v>
+        <v>498252</v>
       </c>
       <c r="R44" t="n">
-        <v>7040344</v>
+        <v>7040210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6175,7 +6154,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6184,12 +6163,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131889803</v>
+        <v>131889541</v>
       </c>
       <c r="B48" t="n">
-        <v>57904</v>
+        <v>78278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6605,31 +6605,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6637,10 +6632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>498061</v>
+        <v>498162</v>
       </c>
       <c r="R48" t="n">
-        <v>7040333</v>
+        <v>7040231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6675,17 +6670,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6696,7 +6687,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6709,14 +6700,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6734,7 +6720,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889798</v>
+        <v>131889803</v>
       </c>
       <c r="B49" t="n">
         <v>57904</v>
@@ -6777,10 +6763,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498109</v>
+        <v>498061</v>
       </c>
       <c r="R49" t="n">
-        <v>7040366</v>
+        <v>7040333</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6874,10 +6860,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131889541</v>
+        <v>131889798</v>
       </c>
       <c r="B50" t="n">
-        <v>78278</v>
+        <v>57904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6885,26 +6871,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6912,10 +6903,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>498162</v>
+        <v>498109</v>
       </c>
       <c r="R50" t="n">
-        <v>7040231</v>
+        <v>7040366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6950,13 +6941,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6967,7 +6962,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6980,9 +6975,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889538</v>
+        <v>131889536</v>
       </c>
       <c r="B71" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9604,16 +9604,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9626,7 +9626,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498308</v>
+        <v>498140</v>
       </c>
       <c r="R71" t="n">
-        <v>7040314</v>
+        <v>7040150</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska hackspår.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9691,6 +9691,11 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9723,10 +9728,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889860</v>
+        <v>131889538</v>
       </c>
       <c r="B72" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9734,26 +9739,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9761,10 +9771,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>498192</v>
+        <v>498308</v>
       </c>
       <c r="R72" t="n">
-        <v>7040190</v>
+        <v>7040314</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9801,7 +9811,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9810,7 +9820,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9849,41 +9858,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889794</v>
+        <v>131889860</v>
       </c>
       <c r="B73" t="n">
-        <v>92561</v>
+        <v>79266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9891,10 +9896,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498247</v>
+        <v>498192</v>
       </c>
       <c r="R73" t="n">
-        <v>7040357</v>
+        <v>7040190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9929,6 +9934,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9941,12 +9951,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9979,40 +9984,39 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889536</v>
+        <v>131889794</v>
       </c>
       <c r="B74" t="n">
-        <v>57904</v>
+        <v>92561</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10022,10 +10026,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498140</v>
+        <v>498247</v>
       </c>
       <c r="R74" t="n">
-        <v>7040150</v>
+        <v>7040357</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10060,23 +10064,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -1410,41 +1410,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888258</v>
+        <v>131889570</v>
       </c>
       <c r="B8" t="n">
-        <v>91801</v>
+        <v>83112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1452,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498240</v>
+        <v>498129</v>
       </c>
       <c r="R8" t="n">
-        <v>7040291</v>
+        <v>7040319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,6 +1501,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1517,12 +1518,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1540,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131889555</v>
+        <v>131888262</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,24 +1552,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1578,10 +1584,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498078</v>
+        <v>497936</v>
       </c>
       <c r="R9" t="n">
-        <v>7040055</v>
+        <v>7040038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,13 +1622,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1661,40 +1671,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888262</v>
+        <v>131888258</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1704,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497936</v>
+        <v>498240</v>
       </c>
       <c r="R10" t="n">
-        <v>7040038</v>
+        <v>7040291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,17 +1751,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1771,9 +1776,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1791,10 +1801,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131889570</v>
+        <v>131889555</v>
       </c>
       <c r="B11" t="n">
-        <v>83112</v>
+        <v>91858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,26 +1812,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1829,10 +1839,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498129</v>
+        <v>498078</v>
       </c>
       <c r="R11" t="n">
-        <v>7040319</v>
+        <v>7040055</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1882,11 +1892,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1897,14 +1902,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888265</v>
+        <v>131888296</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,29 +3233,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3265,10 +3264,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498010</v>
+        <v>498076</v>
       </c>
       <c r="R22" t="n">
-        <v>7040021</v>
+        <v>7040326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3305,7 +3304,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3314,6 +3313,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131888296</v>
+        <v>131889564</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,30 +3363,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3394,10 +3390,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498076</v>
+        <v>498048</v>
       </c>
       <c r="R23" t="n">
-        <v>7040326</v>
+        <v>7040043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3434,7 +3430,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3452,6 +3448,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3462,9 +3463,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3482,10 +3488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131889564</v>
+        <v>131888265</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3493,26 +3499,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3520,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498048</v>
+        <v>498010</v>
       </c>
       <c r="R24" t="n">
-        <v>7040043</v>
+        <v>7040021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3560,7 +3571,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3569,7 +3580,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3578,11 +3588,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3593,14 +3598,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B27" t="n">
-        <v>83112</v>
+        <v>83246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R27" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,6 +3960,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3990,9 +3995,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4010,10 +4020,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B28" t="n">
-        <v>83246</v>
+        <v>83112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4021,21 +4031,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4048,10 +4058,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R28" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4086,11 +4096,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4121,14 +4126,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131889548</v>
+        <v>131888268</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,28 +4548,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4579,10 +4580,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498083</v>
+        <v>498140</v>
       </c>
       <c r="R32" t="n">
-        <v>7040302</v>
+        <v>7040032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4617,13 +4618,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4642,9 +4647,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4662,10 +4672,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888318</v>
+        <v>131889548</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>91834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4673,26 +4683,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4700,10 +4714,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498079</v>
+        <v>498083</v>
       </c>
       <c r="R33" t="n">
-        <v>7040353</v>
+        <v>7040302</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4736,11 +4750,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4788,7 +4797,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888308</v>
+        <v>131888318</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4826,10 +4835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497942</v>
+        <v>498079</v>
       </c>
       <c r="R34" t="n">
-        <v>7040052</v>
+        <v>7040353</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4866,7 +4875,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4914,10 +4923,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888268</v>
+        <v>131888308</v>
       </c>
       <c r="B35" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4925,31 +4934,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4957,10 +4961,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498140</v>
+        <v>497942</v>
       </c>
       <c r="R35" t="n">
-        <v>7040032</v>
+        <v>7040052</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4997,7 +5001,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5006,6 +5010,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5024,14 +5029,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888295</v>
+        <v>131888286</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>80371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498147</v>
+        <v>498252</v>
       </c>
       <c r="R42" t="n">
-        <v>7040335</v>
+        <v>7040210</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,40 +5957,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888279</v>
+        <v>131888295</v>
       </c>
       <c r="B43" t="n">
-        <v>57092</v>
+        <v>91834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6000,10 +5999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498136</v>
+        <v>498147</v>
       </c>
       <c r="R43" t="n">
-        <v>7040344</v>
+        <v>7040335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6040,7 +6039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6049,12 +6048,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6072,39 +6092,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888286</v>
+        <v>131888279</v>
       </c>
       <c r="B44" t="n">
-        <v>80371</v>
+        <v>57092</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6114,10 +6135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498252</v>
+        <v>498136</v>
       </c>
       <c r="R44" t="n">
-        <v>7040210</v>
+        <v>7040344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6154,7 +6175,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6163,33 +6184,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -7768,42 +7768,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889801</v>
+        <v>131889824</v>
       </c>
       <c r="B57" t="n">
-        <v>57904</v>
+        <v>83237</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7811,10 +7806,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>498071</v>
+        <v>498306</v>
       </c>
       <c r="R57" t="n">
-        <v>7040353</v>
+        <v>7040323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7849,17 +7844,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7871,26 +7862,6 @@
       <c r="AI57" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7908,10 +7879,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131889544</v>
+        <v>131889842</v>
       </c>
       <c r="B58" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7919,26 +7890,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7946,10 +7917,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>498103</v>
+        <v>498010</v>
       </c>
       <c r="R58" t="n">
-        <v>7040280</v>
+        <v>7040140</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8001,7 +7972,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8034,37 +8005,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889824</v>
+        <v>131889801</v>
       </c>
       <c r="B59" t="n">
-        <v>83237</v>
+        <v>57904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8072,10 +8048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498306</v>
+        <v>498071</v>
       </c>
       <c r="R59" t="n">
-        <v>7040323</v>
+        <v>7040353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8110,13 +8086,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8128,6 +8108,26 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889842</v>
+        <v>131889544</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8156,26 +8156,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498010</v>
+        <v>498103</v>
       </c>
       <c r="R60" t="n">
-        <v>7040140</v>
+        <v>7040280</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8667,10 +8667,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889879</v>
+        <v>131889862</v>
       </c>
       <c r="B64" t="n">
-        <v>89223</v>
+        <v>79266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8678,30 +8678,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8709,10 +8705,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>498139</v>
+        <v>498155</v>
       </c>
       <c r="R64" t="n">
-        <v>7040231</v>
+        <v>7040384</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8747,6 +8743,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8777,14 +8778,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8802,10 +8798,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889862</v>
+        <v>131889879</v>
       </c>
       <c r="B65" t="n">
-        <v>79266</v>
+        <v>89223</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8813,26 +8809,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>498155</v>
+        <v>498139</v>
       </c>
       <c r="R65" t="n">
-        <v>7040384</v>
+        <v>7040231</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8878,11 +8878,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8913,9 +8908,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889846</v>
+        <v>131889537</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,24 +9074,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9101,10 +9106,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498217</v>
+        <v>498206</v>
       </c>
       <c r="R67" t="n">
-        <v>7040214</v>
+        <v>7040254</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9139,13 +9144,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9154,6 +9163,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9164,9 +9178,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9184,10 +9203,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889858</v>
+        <v>131889846</v>
       </c>
       <c r="B68" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9195,34 +9214,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9230,10 +9241,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498181</v>
+        <v>498217</v>
       </c>
       <c r="R68" t="n">
-        <v>7040135</v>
+        <v>7040214</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9268,11 +9279,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Särskilt rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9285,7 +9291,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9298,14 +9304,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9323,10 +9324,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889537</v>
+        <v>131889858</v>
       </c>
       <c r="B69" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9334,31 +9335,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9366,10 +9370,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498206</v>
+        <v>498181</v>
       </c>
       <c r="R69" t="n">
-        <v>7040254</v>
+        <v>7040135</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9406,7 +9410,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Särskilt rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9415,17 +9419,13 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888266</v>
+        <v>131888314</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1058,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498035</v>
+        <v>498244</v>
       </c>
       <c r="R5" t="n">
-        <v>7040010</v>
+        <v>7040234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131888314</v>
+        <v>131888266</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,26 +1184,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,10 +1216,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498244</v>
+        <v>498035</v>
       </c>
       <c r="R6" t="n">
-        <v>7040234</v>
+        <v>7040010</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1265,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B27" t="n">
-        <v>83246</v>
+        <v>83112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R27" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,11 +3960,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3995,14 +3990,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4020,10 +4010,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B28" t="n">
-        <v>83112</v>
+        <v>83246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4031,21 +4021,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4058,10 +4048,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R28" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4096,6 +4086,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4126,9 +4121,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131888268</v>
+        <v>131889548</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,29 +4548,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4580,10 +4579,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498140</v>
+        <v>498083</v>
       </c>
       <c r="R32" t="n">
-        <v>7040032</v>
+        <v>7040302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4618,17 +4617,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4647,14 +4642,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4672,10 +4662,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131889548</v>
+        <v>131888318</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4683,30 +4673,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4714,10 +4700,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498083</v>
+        <v>498079</v>
       </c>
       <c r="R33" t="n">
-        <v>7040302</v>
+        <v>7040353</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4750,6 +4736,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4797,7 +4788,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888318</v>
+        <v>131888308</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4835,10 +4826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498079</v>
+        <v>497942</v>
       </c>
       <c r="R34" t="n">
-        <v>7040353</v>
+        <v>7040052</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4875,7 +4866,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4923,10 +4914,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888308</v>
+        <v>131888268</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4934,26 +4925,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4961,10 +4957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497942</v>
+        <v>498140</v>
       </c>
       <c r="R35" t="n">
-        <v>7040052</v>
+        <v>7040032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5001,7 +4997,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5010,7 +5006,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5029,9 +5024,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888286</v>
+        <v>131888295</v>
       </c>
       <c r="B42" t="n">
-        <v>80371</v>
+        <v>91834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498252</v>
+        <v>498147</v>
       </c>
       <c r="R42" t="n">
-        <v>7040210</v>
+        <v>7040335</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,39 +5957,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888295</v>
+        <v>131888279</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>57092</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5999,10 +6000,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498147</v>
+        <v>498136</v>
       </c>
       <c r="R43" t="n">
-        <v>7040335</v>
+        <v>7040344</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6039,7 +6040,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6048,33 +6049,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6092,40 +6072,39 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888279</v>
+        <v>131888286</v>
       </c>
       <c r="B44" t="n">
-        <v>57092</v>
+        <v>80371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6135,10 +6114,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498136</v>
+        <v>498252</v>
       </c>
       <c r="R44" t="n">
-        <v>7040344</v>
+        <v>7040210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6175,7 +6154,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6184,12 +6163,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -7768,37 +7768,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889824</v>
+        <v>131889801</v>
       </c>
       <c r="B57" t="n">
-        <v>83237</v>
+        <v>57904</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7806,10 +7811,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>498306</v>
+        <v>498071</v>
       </c>
       <c r="R57" t="n">
-        <v>7040323</v>
+        <v>7040353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7844,13 +7849,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7862,6 +7871,26 @@
       <c r="AI57" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7879,10 +7908,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131889842</v>
+        <v>131889544</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7890,26 +7919,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7917,10 +7946,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>498010</v>
+        <v>498103</v>
       </c>
       <c r="R58" t="n">
-        <v>7040140</v>
+        <v>7040280</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7972,7 +8001,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8005,42 +8034,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889801</v>
+        <v>131889824</v>
       </c>
       <c r="B59" t="n">
-        <v>57904</v>
+        <v>83237</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8048,10 +8072,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498071</v>
+        <v>498306</v>
       </c>
       <c r="R59" t="n">
-        <v>7040353</v>
+        <v>7040323</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8086,17 +8110,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8108,26 +8128,6 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889544</v>
+        <v>131889842</v>
       </c>
       <c r="B60" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8156,26 +8156,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498103</v>
+        <v>498010</v>
       </c>
       <c r="R60" t="n">
-        <v>7040280</v>
+        <v>7040140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889537</v>
+        <v>131889846</v>
       </c>
       <c r="B67" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,29 +9074,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498206</v>
+        <v>498217</v>
       </c>
       <c r="R67" t="n">
-        <v>7040254</v>
+        <v>7040214</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9144,17 +9139,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9163,11 +9154,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9178,14 +9164,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9203,10 +9184,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889846</v>
+        <v>131889858</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9214,26 +9195,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9241,10 +9230,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498217</v>
+        <v>498181</v>
       </c>
       <c r="R68" t="n">
-        <v>7040214</v>
+        <v>7040135</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9279,6 +9268,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Särskilt rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9291,7 +9285,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9304,9 +9298,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9324,10 +9323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889858</v>
+        <v>131889537</v>
       </c>
       <c r="B69" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9335,34 +9334,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9370,10 +9366,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498181</v>
+        <v>498206</v>
       </c>
       <c r="R69" t="n">
-        <v>7040135</v>
+        <v>7040254</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9410,7 +9406,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Särskilt rikligt med garnlav här!</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9419,13 +9415,17 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889536</v>
+        <v>131889538</v>
       </c>
       <c r="B71" t="n">
-        <v>57904</v>
+        <v>57901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9604,16 +9604,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9626,7 +9626,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498140</v>
+        <v>498308</v>
       </c>
       <c r="R71" t="n">
-        <v>7040150</v>
+        <v>7040314</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9691,11 +9691,6 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9728,10 +9723,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889538</v>
+        <v>131889860</v>
       </c>
       <c r="B72" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9739,31 +9734,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9771,10 +9761,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>498308</v>
+        <v>498192</v>
       </c>
       <c r="R72" t="n">
-        <v>7040314</v>
+        <v>7040190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9811,7 +9801,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska hackspår.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9820,6 +9810,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9858,37 +9849,41 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889860</v>
+        <v>131889794</v>
       </c>
       <c r="B73" t="n">
-        <v>79266</v>
+        <v>92561</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9896,10 +9891,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498192</v>
+        <v>498247</v>
       </c>
       <c r="R73" t="n">
-        <v>7040190</v>
+        <v>7040357</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9934,11 +9929,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9951,7 +9941,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9984,39 +9979,40 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889794</v>
+        <v>131889536</v>
       </c>
       <c r="B74" t="n">
-        <v>92561</v>
+        <v>57904</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10026,10 +10022,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498247</v>
+        <v>498140</v>
       </c>
       <c r="R74" t="n">
-        <v>7040357</v>
+        <v>7040150</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10064,19 +10060,23 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
@@ -10375,32 +10375,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889825</v>
+        <v>131889833</v>
       </c>
       <c r="B77" t="n">
-        <v>92298</v>
+        <v>91834</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10417,10 +10417,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498076</v>
+        <v>498237</v>
       </c>
       <c r="R77" t="n">
-        <v>7040226</v>
+        <v>7040342</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889833</v>
+        <v>131889788</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
+        <v>91838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498237</v>
+        <v>498075</v>
       </c>
       <c r="R78" t="n">
-        <v>7040342</v>
+        <v>7040043</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10635,32 +10635,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889788</v>
+        <v>131889841</v>
       </c>
       <c r="B79" t="n">
-        <v>91838</v>
+        <v>92212</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>498075</v>
+        <v>498085</v>
       </c>
       <c r="R79" t="n">
-        <v>7040043</v>
+        <v>7040081</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10737,17 +10737,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10765,39 +10770,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131889841</v>
+        <v>131889800</v>
       </c>
       <c r="B80" t="n">
-        <v>92212</v>
+        <v>57904</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -10807,10 +10813,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>498085</v>
+        <v>498089</v>
       </c>
       <c r="R80" t="n">
-        <v>7040081</v>
+        <v>7040360</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10845,13 +10851,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10867,22 +10877,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10900,40 +10910,39 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131889800</v>
+        <v>131889825</v>
       </c>
       <c r="B81" t="n">
-        <v>57904</v>
+        <v>92298</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10943,10 +10952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498089</v>
+        <v>498076</v>
       </c>
       <c r="R81" t="n">
-        <v>7040360</v>
+        <v>7040226</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10981,17 +10990,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11015,14 +11020,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B27" t="n">
-        <v>83112</v>
+        <v>83246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R27" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,6 +3960,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3990,9 +3995,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4010,10 +4020,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B28" t="n">
-        <v>83246</v>
+        <v>83112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4021,21 +4031,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4048,10 +4058,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R28" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4086,11 +4096,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4121,14 +4126,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888295</v>
+        <v>131888286</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>80371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498147</v>
+        <v>498252</v>
       </c>
       <c r="R42" t="n">
-        <v>7040335</v>
+        <v>7040210</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,40 +5957,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888279</v>
+        <v>131888295</v>
       </c>
       <c r="B43" t="n">
-        <v>57092</v>
+        <v>91834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6000,10 +5999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498136</v>
+        <v>498147</v>
       </c>
       <c r="R43" t="n">
-        <v>7040344</v>
+        <v>7040335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6040,7 +6039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6049,12 +6048,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6072,39 +6092,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888286</v>
+        <v>131888279</v>
       </c>
       <c r="B44" t="n">
-        <v>80371</v>
+        <v>57092</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6114,10 +6135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498252</v>
+        <v>498136</v>
       </c>
       <c r="R44" t="n">
-        <v>7040210</v>
+        <v>7040344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6154,7 +6175,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6163,33 +6184,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131889541</v>
+        <v>131889803</v>
       </c>
       <c r="B48" t="n">
-        <v>78278</v>
+        <v>57904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6605,26 +6605,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6632,10 +6637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>498162</v>
+        <v>498061</v>
       </c>
       <c r="R48" t="n">
-        <v>7040231</v>
+        <v>7040333</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6670,13 +6675,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6687,7 +6696,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6700,9 +6709,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6720,7 +6734,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889803</v>
+        <v>131889798</v>
       </c>
       <c r="B49" t="n">
         <v>57904</v>
@@ -6763,10 +6777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498061</v>
+        <v>498109</v>
       </c>
       <c r="R49" t="n">
-        <v>7040333</v>
+        <v>7040366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6860,10 +6874,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131889798</v>
+        <v>131889541</v>
       </c>
       <c r="B50" t="n">
-        <v>57904</v>
+        <v>78278</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6871,31 +6885,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6903,10 +6912,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>498109</v>
+        <v>498162</v>
       </c>
       <c r="R50" t="n">
-        <v>7040366</v>
+        <v>7040231</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6941,17 +6950,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6962,7 +6967,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6975,14 +6980,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131889854</v>
+        <v>131889535</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7011,24 +7011,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7038,10 +7043,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>498128</v>
+        <v>497945</v>
       </c>
       <c r="R51" t="n">
-        <v>7040149</v>
+        <v>7040123</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7076,13 +7081,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7106,9 +7115,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7126,10 +7140,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889535</v>
+        <v>131889854</v>
       </c>
       <c r="B52" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7137,29 +7151,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7169,10 +7178,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497945</v>
+        <v>498128</v>
       </c>
       <c r="R52" t="n">
-        <v>7040123</v>
+        <v>7040149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7207,17 +7216,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7241,14 +7246,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889538</v>
+        <v>131889536</v>
       </c>
       <c r="B71" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9604,16 +9604,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9626,7 +9626,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498308</v>
+        <v>498140</v>
       </c>
       <c r="R71" t="n">
-        <v>7040314</v>
+        <v>7040150</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska hackspår.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9691,6 +9691,11 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9723,10 +9728,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889860</v>
+        <v>131889538</v>
       </c>
       <c r="B72" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9734,26 +9739,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9761,10 +9771,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>498192</v>
+        <v>498308</v>
       </c>
       <c r="R72" t="n">
-        <v>7040190</v>
+        <v>7040314</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9801,7 +9811,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9810,7 +9820,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9849,41 +9858,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889794</v>
+        <v>131889860</v>
       </c>
       <c r="B73" t="n">
-        <v>92561</v>
+        <v>79266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9891,10 +9896,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498247</v>
+        <v>498192</v>
       </c>
       <c r="R73" t="n">
-        <v>7040357</v>
+        <v>7040190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9929,6 +9934,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9941,12 +9951,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9979,40 +9984,39 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889536</v>
+        <v>131889794</v>
       </c>
       <c r="B74" t="n">
-        <v>57904</v>
+        <v>92561</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10022,10 +10026,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498140</v>
+        <v>498247</v>
       </c>
       <c r="R74" t="n">
-        <v>7040150</v>
+        <v>7040357</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10060,23 +10064,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888314</v>
+        <v>131888266</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,26 +1058,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498244</v>
+        <v>498035</v>
       </c>
       <c r="R5" t="n">
-        <v>7040234</v>
+        <v>7040010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1139,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131888266</v>
+        <v>131888314</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,31 +1188,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1216,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498035</v>
+        <v>498244</v>
       </c>
       <c r="R6" t="n">
-        <v>7040010</v>
+        <v>7040234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1255,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1264,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131889535</v>
+        <v>131889854</v>
       </c>
       <c r="B51" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7011,29 +7011,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7043,10 +7038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497945</v>
+        <v>498128</v>
       </c>
       <c r="R51" t="n">
-        <v>7040123</v>
+        <v>7040149</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7081,17 +7076,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7115,14 +7106,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7140,10 +7126,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889854</v>
+        <v>131889535</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7151,24 +7137,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7178,10 +7169,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>498128</v>
+        <v>497945</v>
       </c>
       <c r="R52" t="n">
-        <v>7040149</v>
+        <v>7040123</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7216,13 +7207,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7246,9 +7241,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -8667,10 +8667,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889862</v>
+        <v>131889879</v>
       </c>
       <c r="B64" t="n">
-        <v>79266</v>
+        <v>89223</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8678,26 +8678,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8705,10 +8709,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>498155</v>
+        <v>498139</v>
       </c>
       <c r="R64" t="n">
-        <v>7040384</v>
+        <v>7040231</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8743,11 +8747,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8778,9 +8777,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8798,10 +8802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889879</v>
+        <v>131889862</v>
       </c>
       <c r="B65" t="n">
-        <v>89223</v>
+        <v>79266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8809,30 +8813,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>498139</v>
+        <v>498155</v>
       </c>
       <c r="R65" t="n">
-        <v>7040231</v>
+        <v>7040384</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8878,6 +8878,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8908,14 +8913,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889846</v>
+        <v>131889537</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,24 +9074,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9101,10 +9106,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498217</v>
+        <v>498206</v>
       </c>
       <c r="R67" t="n">
-        <v>7040214</v>
+        <v>7040254</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9139,13 +9144,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9154,6 +9163,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9164,9 +9178,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9184,10 +9203,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889858</v>
+        <v>131889846</v>
       </c>
       <c r="B68" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9195,34 +9214,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9230,10 +9241,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498181</v>
+        <v>498217</v>
       </c>
       <c r="R68" t="n">
-        <v>7040135</v>
+        <v>7040214</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9268,11 +9279,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Särskilt rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9285,7 +9291,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9298,14 +9304,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9323,10 +9324,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889537</v>
+        <v>131889858</v>
       </c>
       <c r="B69" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9334,31 +9335,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9366,10 +9370,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498206</v>
+        <v>498181</v>
       </c>
       <c r="R69" t="n">
-        <v>7040254</v>
+        <v>7040135</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9406,7 +9410,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Särskilt rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9415,17 +9419,13 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888266</v>
+        <v>131888314</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1058,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498035</v>
+        <v>498244</v>
       </c>
       <c r="R5" t="n">
-        <v>7040010</v>
+        <v>7040234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131888314</v>
+        <v>131888266</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,26 +1184,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,10 +1216,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498244</v>
+        <v>498035</v>
       </c>
       <c r="R6" t="n">
-        <v>7040234</v>
+        <v>7040010</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1265,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1410,37 +1410,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131889570</v>
+        <v>131888258</v>
       </c>
       <c r="B8" t="n">
-        <v>83112</v>
+        <v>91801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498129</v>
+        <v>498240</v>
       </c>
       <c r="R8" t="n">
-        <v>7040319</v>
+        <v>7040291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,11 +1505,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1518,12 +1517,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1541,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888262</v>
+        <v>131889555</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,29 +1551,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1584,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497936</v>
+        <v>498078</v>
       </c>
       <c r="R9" t="n">
-        <v>7040038</v>
+        <v>7040055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1622,17 +1616,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1671,39 +1661,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888258</v>
+        <v>131888262</v>
       </c>
       <c r="B10" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1713,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498240</v>
+        <v>497936</v>
       </c>
       <c r="R10" t="n">
-        <v>7040291</v>
+        <v>7040038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,13 +1742,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1776,14 +1771,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1801,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131889555</v>
+        <v>131889570</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>83112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,26 +1802,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1839,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498078</v>
+        <v>498129</v>
       </c>
       <c r="R11" t="n">
-        <v>7040055</v>
+        <v>7040319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1892,6 +1882,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1902,9 +1897,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B27" t="n">
-        <v>83246</v>
+        <v>83112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R27" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,11 +3960,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3995,14 +3990,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4020,10 +4010,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B28" t="n">
-        <v>83112</v>
+        <v>83246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4031,21 +4021,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4058,10 +4048,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R28" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4096,6 +4086,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4126,9 +4121,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888286</v>
+        <v>131888295</v>
       </c>
       <c r="B42" t="n">
-        <v>80371</v>
+        <v>91834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498252</v>
+        <v>498147</v>
       </c>
       <c r="R42" t="n">
-        <v>7040210</v>
+        <v>7040335</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,39 +5957,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888295</v>
+        <v>131888279</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>57092</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5999,10 +6000,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498147</v>
+        <v>498136</v>
       </c>
       <c r="R43" t="n">
-        <v>7040335</v>
+        <v>7040344</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6039,7 +6040,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6048,33 +6049,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6092,40 +6072,39 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888279</v>
+        <v>131888286</v>
       </c>
       <c r="B44" t="n">
-        <v>57092</v>
+        <v>80371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6135,10 +6114,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498136</v>
+        <v>498252</v>
       </c>
       <c r="R44" t="n">
-        <v>7040344</v>
+        <v>7040210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6175,7 +6154,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6184,12 +6163,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131889854</v>
+        <v>131889535</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7011,24 +7011,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7038,10 +7043,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>498128</v>
+        <v>497945</v>
       </c>
       <c r="R51" t="n">
-        <v>7040149</v>
+        <v>7040123</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7076,13 +7081,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7106,9 +7115,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7126,10 +7140,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889535</v>
+        <v>131889854</v>
       </c>
       <c r="B52" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7137,29 +7151,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7169,10 +7178,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497945</v>
+        <v>498128</v>
       </c>
       <c r="R52" t="n">
-        <v>7040123</v>
+        <v>7040149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7207,17 +7216,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7241,14 +7246,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7768,42 +7768,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889801</v>
+        <v>131889824</v>
       </c>
       <c r="B57" t="n">
-        <v>57904</v>
+        <v>83237</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7811,10 +7806,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>498071</v>
+        <v>498306</v>
       </c>
       <c r="R57" t="n">
-        <v>7040353</v>
+        <v>7040323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7849,17 +7844,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7871,26 +7862,6 @@
       <c r="AI57" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7908,10 +7879,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131889544</v>
+        <v>131889842</v>
       </c>
       <c r="B58" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7919,26 +7890,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7946,10 +7917,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>498103</v>
+        <v>498010</v>
       </c>
       <c r="R58" t="n">
-        <v>7040280</v>
+        <v>7040140</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8001,7 +7972,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8034,37 +8005,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889824</v>
+        <v>131889801</v>
       </c>
       <c r="B59" t="n">
-        <v>83237</v>
+        <v>57904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8072,10 +8048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498306</v>
+        <v>498071</v>
       </c>
       <c r="R59" t="n">
-        <v>7040323</v>
+        <v>7040353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8110,13 +8086,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8128,6 +8108,26 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889842</v>
+        <v>131889544</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8156,26 +8156,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498010</v>
+        <v>498103</v>
       </c>
       <c r="R60" t="n">
-        <v>7040140</v>
+        <v>7040280</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889537</v>
+        <v>131889846</v>
       </c>
       <c r="B67" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,29 +9074,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498206</v>
+        <v>498217</v>
       </c>
       <c r="R67" t="n">
-        <v>7040254</v>
+        <v>7040214</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9144,17 +9139,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9163,11 +9154,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9178,14 +9164,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9203,10 +9184,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889846</v>
+        <v>131889858</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9214,26 +9195,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9241,10 +9230,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498217</v>
+        <v>498181</v>
       </c>
       <c r="R68" t="n">
-        <v>7040214</v>
+        <v>7040135</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9279,6 +9268,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Särskilt rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9291,7 +9285,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9304,9 +9298,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9324,10 +9323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889858</v>
+        <v>131889537</v>
       </c>
       <c r="B69" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9335,34 +9334,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9370,10 +9366,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498181</v>
+        <v>498206</v>
       </c>
       <c r="R69" t="n">
-        <v>7040135</v>
+        <v>7040254</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9410,7 +9406,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Särskilt rikligt med garnlav här!</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9419,13 +9415,17 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -10375,32 +10375,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889833</v>
+        <v>131889825</v>
       </c>
       <c r="B77" t="n">
-        <v>91834</v>
+        <v>92298</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10417,10 +10417,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498237</v>
+        <v>498076</v>
       </c>
       <c r="R77" t="n">
-        <v>7040342</v>
+        <v>7040226</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889788</v>
+        <v>131889833</v>
       </c>
       <c r="B78" t="n">
-        <v>91838</v>
+        <v>91834</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498075</v>
+        <v>498237</v>
       </c>
       <c r="R78" t="n">
-        <v>7040043</v>
+        <v>7040342</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10635,32 +10635,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889841</v>
+        <v>131889788</v>
       </c>
       <c r="B79" t="n">
-        <v>92212</v>
+        <v>91838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>498085</v>
+        <v>498075</v>
       </c>
       <c r="R79" t="n">
-        <v>7040081</v>
+        <v>7040043</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10737,22 +10737,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10770,40 +10765,39 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131889800</v>
+        <v>131889841</v>
       </c>
       <c r="B80" t="n">
-        <v>57904</v>
+        <v>92212</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -10813,10 +10807,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>498089</v>
+        <v>498085</v>
       </c>
       <c r="R80" t="n">
-        <v>7040360</v>
+        <v>7040081</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10851,17 +10845,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10877,22 +10867,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10910,39 +10900,40 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131889825</v>
+        <v>131889800</v>
       </c>
       <c r="B81" t="n">
-        <v>92298</v>
+        <v>57904</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10952,10 +10943,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498076</v>
+        <v>498089</v>
       </c>
       <c r="R81" t="n">
-        <v>7040226</v>
+        <v>7040360</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10990,13 +10981,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11020,9 +11015,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>131888264</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131888312</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888314</v>
+        <v>131888266</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,26 +1058,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498244</v>
+        <v>498035</v>
       </c>
       <c r="R5" t="n">
-        <v>7040234</v>
+        <v>7040010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1139,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131888266</v>
+        <v>131888314</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,31 +1188,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1216,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498035</v>
+        <v>498244</v>
       </c>
       <c r="R6" t="n">
-        <v>7040010</v>
+        <v>7040234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1255,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1264,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>131888283</v>
       </c>
       <c r="B7" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,39 +1410,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888258</v>
+        <v>131888262</v>
       </c>
       <c r="B8" t="n">
-        <v>91801</v>
+        <v>57907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1452,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498240</v>
+        <v>497936</v>
       </c>
       <c r="R8" t="n">
-        <v>7040291</v>
+        <v>7040038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,13 +1491,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1515,14 +1520,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1540,30 +1540,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131889555</v>
+        <v>131888258</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>91804</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -1578,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498078</v>
+        <v>498240</v>
       </c>
       <c r="R9" t="n">
-        <v>7040055</v>
+        <v>7040291</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1641,9 +1645,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # En klen granlåga. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1661,10 +1670,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888262</v>
+        <v>131889555</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,29 +1681,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1704,10 +1708,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497936</v>
+        <v>498078</v>
       </c>
       <c r="R10" t="n">
-        <v>7040038</v>
+        <v>7040055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,17 +1746,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>131889570</v>
       </c>
       <c r="B11" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888272</v>
+        <v>131889553</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,29 +1933,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1965,10 +1960,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498063</v>
+        <v>497949</v>
       </c>
       <c r="R12" t="n">
-        <v>7040346</v>
+        <v>7040132</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2003,17 +1998,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2032,14 +2023,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,10 +2043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888294</v>
+        <v>131888272</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>57907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,28 +2054,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2099,10 +2086,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498217</v>
+        <v>498063</v>
       </c>
       <c r="R13" t="n">
-        <v>7040172</v>
+        <v>7040346</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,7 +2126,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,7 +2135,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2155,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2192,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131889553</v>
+        <v>131888294</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,19 +2189,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -2230,10 +2220,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497949</v>
+        <v>498217</v>
       </c>
       <c r="R14" t="n">
-        <v>7040132</v>
+        <v>7040172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2268,6 +2258,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2293,9 +2288,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
         <v>131888270</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131889546</v>
+        <v>131888309</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>79269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,30 +2459,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2490,10 +2486,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498059</v>
+        <v>498001</v>
       </c>
       <c r="R16" t="n">
-        <v>7040135</v>
+        <v>7040034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2528,6 +2524,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på flera granar här.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2543,11 +2544,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2558,9 +2554,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2578,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131888309</v>
+        <v>131889562</v>
       </c>
       <c r="B17" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,10 +2617,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498001</v>
+        <v>498066</v>
       </c>
       <c r="R17" t="n">
-        <v>7040034</v>
+        <v>7040263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2656,7 +2657,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar här.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2672,6 +2673,11 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2709,10 +2715,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131889562</v>
+        <v>131888310</v>
       </c>
       <c r="B18" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,10 +2753,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498066</v>
+        <v>498071</v>
       </c>
       <c r="R18" t="n">
-        <v>7040263</v>
+        <v>7040023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2787,7 +2793,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,11 +2811,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2820,14 +2821,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2845,10 +2841,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131888310</v>
+        <v>131888313</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2883,10 +2879,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498071</v>
+        <v>498228</v>
       </c>
       <c r="R19" t="n">
-        <v>7040023</v>
+        <v>7040198</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2923,7 +2919,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Hyfsat rikligt med garnlavsbålar på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,10 +2967,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131888313</v>
+        <v>131889546</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>91837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,26 +2978,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498228</v>
+        <v>498059</v>
       </c>
       <c r="R20" t="n">
-        <v>7040198</v>
+        <v>7040135</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,11 +3047,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med garnlavsbålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3065,6 +3060,11 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3100,7 +3100,7 @@
         <v>131889547</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888296</v>
+        <v>131888265</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>57907</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,28 +3233,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3264,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498076</v>
+        <v>498010</v>
       </c>
       <c r="R22" t="n">
-        <v>7040326</v>
+        <v>7040021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3304,7 +3305,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,7 +3314,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>131889564</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888265</v>
+        <v>131888296</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>91837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,29 +3499,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3531,10 +3530,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498010</v>
+        <v>498076</v>
       </c>
       <c r="R24" t="n">
-        <v>7040021</v>
+        <v>7040326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3571,7 +3570,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3580,6 +3579,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>131888317</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>131888288</v>
       </c>
       <c r="B26" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B27" t="n">
-        <v>83112</v>
+        <v>83249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R27" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,6 +3960,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3990,9 +3995,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4010,10 +4020,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B28" t="n">
-        <v>83246</v>
+        <v>83115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4021,21 +4031,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4048,10 +4058,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R28" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4086,11 +4096,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4121,14 +4126,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131888263</v>
+        <v>131888269</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497963</v>
+        <v>498161</v>
       </c>
       <c r="R29" t="n">
-        <v>7040031</v>
+        <v>7040066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4256,9 +4256,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4276,10 +4281,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888269</v>
+        <v>131888263</v>
       </c>
       <c r="B30" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498161</v>
+        <v>497963</v>
       </c>
       <c r="R30" t="n">
-        <v>7040066</v>
+        <v>7040031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4359,7 +4364,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4386,14 +4391,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
         <v>131889558</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131889548</v>
+        <v>131888268</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>57907</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,28 +4548,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4579,10 +4580,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498083</v>
+        <v>498140</v>
       </c>
       <c r="R32" t="n">
-        <v>7040302</v>
+        <v>7040032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4617,13 +4618,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4642,9 +4647,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4665,7 +4675,7 @@
         <v>131888318</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4791,7 +4801,7 @@
         <v>131888308</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4914,10 +4924,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888268</v>
+        <v>131889548</v>
       </c>
       <c r="B35" t="n">
-        <v>57904</v>
+        <v>91837</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4925,29 +4935,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4957,10 +4966,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498140</v>
+        <v>498083</v>
       </c>
       <c r="R35" t="n">
-        <v>7040032</v>
+        <v>7040302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4995,17 +5004,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5024,14 +5029,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131888287</v>
+        <v>131888261</v>
       </c>
       <c r="B36" t="n">
-        <v>80371</v>
+        <v>57907</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5060,28 +5060,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5091,10 +5092,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>498148</v>
+        <v>497929</v>
       </c>
       <c r="R36" t="n">
-        <v>7040325</v>
+        <v>7040047</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5131,7 +5132,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5140,7 +5141,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5151,22 +5151,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131889554</v>
+        <v>131888287</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>80374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5195,24 +5195,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5222,10 +5226,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>498048</v>
+        <v>498148</v>
       </c>
       <c r="R37" t="n">
-        <v>7040052</v>
+        <v>7040325</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5260,6 +5264,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5277,17 +5286,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5305,10 +5319,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131888261</v>
+        <v>131889554</v>
       </c>
       <c r="B38" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5316,29 +5330,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5348,10 +5357,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497929</v>
+        <v>498048</v>
       </c>
       <c r="R38" t="n">
-        <v>7040047</v>
+        <v>7040052</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5386,17 +5395,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5415,14 +5420,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131889556</v>
+        <v>131888271</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>57907</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5451,24 +5451,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>498308</v>
+        <v>498306</v>
       </c>
       <c r="R39" t="n">
-        <v>7040314</v>
+        <v>7040264</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5516,13 +5521,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5541,9 +5550,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5561,10 +5575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131888271</v>
+        <v>131889556</v>
       </c>
       <c r="B40" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5572,29 +5586,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5604,10 +5613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>498306</v>
+        <v>498308</v>
       </c>
       <c r="R40" t="n">
-        <v>7040264</v>
+        <v>7040314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5642,17 +5651,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5671,14 +5676,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
         <v>131888316</v>
       </c>
       <c r="B41" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5822,39 +5822,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888295</v>
+        <v>131888279</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>57095</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5865,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498147</v>
+        <v>498136</v>
       </c>
       <c r="R42" t="n">
-        <v>7040335</v>
+        <v>7040344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5905,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5913,33 +5914,12 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,40 +5937,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888279</v>
+        <v>131888286</v>
       </c>
       <c r="B43" t="n">
-        <v>57092</v>
+        <v>80374</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6000,10 +5979,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498136</v>
+        <v>498252</v>
       </c>
       <c r="R43" t="n">
-        <v>7040344</v>
+        <v>7040210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6040,7 +6019,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6049,12 +6028,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888286</v>
+        <v>131888295</v>
       </c>
       <c r="B44" t="n">
-        <v>80371</v>
+        <v>91837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6083,28 +6083,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498252</v>
+        <v>498147</v>
       </c>
       <c r="R44" t="n">
-        <v>7040210</v>
+        <v>7040335</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6174,22 +6174,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
         <v>131888315</v>
       </c>
       <c r="B45" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>131888311</v>
       </c>
       <c r="B46" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131889782</v>
+        <v>131889541</v>
       </c>
       <c r="B47" t="n">
-        <v>91838</v>
+        <v>78281</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6475,30 +6475,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6506,10 +6502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>498206</v>
+        <v>498162</v>
       </c>
       <c r="R47" t="n">
-        <v>7040320</v>
+        <v>7040231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6561,7 +6557,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6594,10 +6590,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131889803</v>
+        <v>131889798</v>
       </c>
       <c r="B48" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6637,10 +6633,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>498061</v>
+        <v>498109</v>
       </c>
       <c r="R48" t="n">
-        <v>7040333</v>
+        <v>7040366</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6734,10 +6730,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889798</v>
+        <v>131889803</v>
       </c>
       <c r="B49" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6777,10 +6773,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498109</v>
+        <v>498061</v>
       </c>
       <c r="R49" t="n">
-        <v>7040366</v>
+        <v>7040333</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6874,10 +6870,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131889541</v>
+        <v>131889782</v>
       </c>
       <c r="B50" t="n">
-        <v>78278</v>
+        <v>91841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6885,26 +6881,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>498162</v>
+        <v>498206</v>
       </c>
       <c r="R50" t="n">
-        <v>7040231</v>
+        <v>7040320</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7003,7 +7003,7 @@
         <v>131889535</v>
       </c>
       <c r="B51" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>131889854</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>131889830</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>131889781</v>
       </c>
       <c r="B54" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131889826</v>
       </c>
       <c r="B55" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>131889822</v>
       </c>
       <c r="B56" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>131889824</v>
       </c>
       <c r="B57" t="n">
-        <v>83237</v>
+        <v>83240</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>131889842</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>131889801</v>
       </c>
       <c r="B59" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>131889544</v>
       </c>
       <c r="B60" t="n">
-        <v>78278</v>
+        <v>78281</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>131889861</v>
       </c>
       <c r="B61" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>131889793</v>
       </c>
       <c r="B62" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>131889792</v>
       </c>
       <c r="B63" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8667,10 +8667,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889879</v>
+        <v>131889862</v>
       </c>
       <c r="B64" t="n">
-        <v>89223</v>
+        <v>79269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8678,30 +8678,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8709,10 +8705,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>498139</v>
+        <v>498155</v>
       </c>
       <c r="R64" t="n">
-        <v>7040231</v>
+        <v>7040384</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8747,6 +8743,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8777,14 +8778,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8802,10 +8798,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889862</v>
+        <v>131889879</v>
       </c>
       <c r="B65" t="n">
-        <v>79266</v>
+        <v>89226</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8813,26 +8809,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>498155</v>
+        <v>498139</v>
       </c>
       <c r="R65" t="n">
-        <v>7040384</v>
+        <v>7040231</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8878,11 +8878,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8913,9 +8908,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8936,7 +8936,7 @@
         <v>131889780</v>
       </c>
       <c r="B66" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889846</v>
+        <v>131889537</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>57907</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,24 +9074,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9101,10 +9106,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498217</v>
+        <v>498206</v>
       </c>
       <c r="R67" t="n">
-        <v>7040214</v>
+        <v>7040254</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9139,13 +9144,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9154,6 +9163,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9164,9 +9178,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9184,10 +9203,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889858</v>
+        <v>131889846</v>
       </c>
       <c r="B68" t="n">
-        <v>79266</v>
+        <v>91861</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9195,34 +9214,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9230,10 +9241,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498181</v>
+        <v>498217</v>
       </c>
       <c r="R68" t="n">
-        <v>7040135</v>
+        <v>7040214</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9268,11 +9279,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Särskilt rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9285,7 +9291,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9298,14 +9304,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9323,10 +9324,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889537</v>
+        <v>131889858</v>
       </c>
       <c r="B69" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9334,31 +9335,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9366,10 +9370,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498206</v>
+        <v>498181</v>
       </c>
       <c r="R69" t="n">
-        <v>7040254</v>
+        <v>7040135</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9406,7 +9410,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Särskilt rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9415,17 +9419,13 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
         <v>131889837</v>
       </c>
       <c r="B70" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889536</v>
+        <v>131889860</v>
       </c>
       <c r="B71" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9604,31 +9604,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9636,10 +9631,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498140</v>
+        <v>498192</v>
       </c>
       <c r="R71" t="n">
-        <v>7040150</v>
+        <v>7040190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9676,7 +9671,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9685,17 +9680,13 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9731,7 +9722,7 @@
         <v>131889538</v>
       </c>
       <c r="B72" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9858,10 +9849,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889860</v>
+        <v>131889536</v>
       </c>
       <c r="B73" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9869,26 +9860,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9896,10 +9892,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498192</v>
+        <v>498140</v>
       </c>
       <c r="R73" t="n">
-        <v>7040190</v>
+        <v>7040150</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9936,7 +9932,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9945,13 +9941,17 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9987,7 +9987,7 @@
         <v>131889794</v>
       </c>
       <c r="B74" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>131889843</v>
       </c>
       <c r="B75" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>131889799</v>
       </c>
       <c r="B76" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10375,39 +10375,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889825</v>
+        <v>131889800</v>
       </c>
       <c r="B77" t="n">
-        <v>92298</v>
+        <v>57907</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10417,10 +10418,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498076</v>
+        <v>498089</v>
       </c>
       <c r="R77" t="n">
-        <v>7040226</v>
+        <v>7040360</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10455,13 +10456,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10485,9 +10490,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10505,32 +10515,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889833</v>
+        <v>131889825</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
+        <v>92301</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10547,10 +10557,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498237</v>
+        <v>498076</v>
       </c>
       <c r="R78" t="n">
-        <v>7040342</v>
+        <v>7040226</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10635,10 +10645,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889788</v>
+        <v>131889833</v>
       </c>
       <c r="B79" t="n">
-        <v>91838</v>
+        <v>91837</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10646,21 +10656,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10677,10 +10687,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>498075</v>
+        <v>498237</v>
       </c>
       <c r="R79" t="n">
-        <v>7040043</v>
+        <v>7040342</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10765,32 +10775,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131889841</v>
+        <v>131889788</v>
       </c>
       <c r="B80" t="n">
-        <v>92212</v>
+        <v>91841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10807,10 +10817,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>498085</v>
+        <v>498075</v>
       </c>
       <c r="R80" t="n">
-        <v>7040081</v>
+        <v>7040043</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10867,22 +10877,17 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10900,40 +10905,39 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131889800</v>
+        <v>131889841</v>
       </c>
       <c r="B81" t="n">
-        <v>57904</v>
+        <v>92215</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10943,10 +10947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498089</v>
+        <v>498085</v>
       </c>
       <c r="R81" t="n">
-        <v>7040360</v>
+        <v>7040081</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10981,17 +10985,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11007,22 +11007,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11043,7 +11043,7 @@
         <v>131889787</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>131889857</v>
       </c>
       <c r="B83" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>131889844</v>
       </c>
       <c r="B84" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11427,10 +11427,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889779</v>
+        <v>131889845</v>
       </c>
       <c r="B85" t="n">
-        <v>91838</v>
+        <v>91861</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11438,23 +11438,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -11469,10 +11465,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>498070</v>
+        <v>498096</v>
       </c>
       <c r="R85" t="n">
-        <v>7040031</v>
+        <v>7040105</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11537,14 +11533,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11565,7 +11556,7 @@
         <v>131889539</v>
       </c>
       <c r="B86" t="n">
-        <v>83237</v>
+        <v>83240</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11673,10 +11664,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889529</v>
+        <v>131889779</v>
       </c>
       <c r="B87" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11715,10 +11706,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>498137</v>
+        <v>498070</v>
       </c>
       <c r="R87" t="n">
-        <v>7040255</v>
+        <v>7040031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11783,9 +11774,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11803,10 +11799,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889845</v>
+        <v>131889529</v>
       </c>
       <c r="B88" t="n">
-        <v>91858</v>
+        <v>91841</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11814,19 +11810,23 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>498096</v>
+        <v>498137</v>
       </c>
       <c r="R88" t="n">
-        <v>7040105</v>
+        <v>7040255</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11932,7 +11932,7 @@
         <v>131889877</v>
       </c>
       <c r="B89" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>131888264</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131888312</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,42 +1047,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888266</v>
+        <v>131888283</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>97917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498035</v>
+        <v>498177</v>
       </c>
       <c r="R5" t="n">
-        <v>7040010</v>
+        <v>7040311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,38 +1124,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,7 +1157,7 @@
         <v>131888314</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,38 +1280,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888283</v>
+        <v>131888266</v>
       </c>
       <c r="B7" t="n">
-        <v>97912</v>
+        <v>57912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1342,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498177</v>
+        <v>498035</v>
       </c>
       <c r="R7" t="n">
-        <v>7040311</v>
+        <v>7040010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,19 +1361,38 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888262</v>
+        <v>131889570</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>83120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,31 +1421,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1453,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497936</v>
+        <v>498129</v>
       </c>
       <c r="R8" t="n">
-        <v>7040038</v>
+        <v>7040319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,17 +1486,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1510,6 +1501,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1520,9 +1516,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,7 +1544,7 @@
         <v>131888258</v>
       </c>
       <c r="B9" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1674,7 @@
         <v>131889555</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,10 +1792,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131889570</v>
+        <v>131888262</v>
       </c>
       <c r="B11" t="n">
-        <v>83115</v>
+        <v>57912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,26 +1803,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1829,10 +1835,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498129</v>
+        <v>497936</v>
       </c>
       <c r="R11" t="n">
-        <v>7040319</v>
+        <v>7040038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,13 +1873,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1882,11 +1892,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1897,14 +1902,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1925,7 +1925,7 @@
         <v>131889553</v>
       </c>
       <c r="B12" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888272</v>
+        <v>131888294</v>
       </c>
       <c r="B13" t="n">
-        <v>57907</v>
+        <v>91842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,29 +2054,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2086,10 +2085,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498063</v>
+        <v>498217</v>
       </c>
       <c r="R13" t="n">
-        <v>7040346</v>
+        <v>7040172</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2126,7 +2125,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,6 +2134,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131888294</v>
+        <v>131888272</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>57912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,28 +2189,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2220,10 +2221,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498217</v>
+        <v>498063</v>
       </c>
       <c r="R14" t="n">
-        <v>7040172</v>
+        <v>7040346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2261,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,7 +2270,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
         <v>131888270</v>
       </c>
       <c r="B15" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>131888309</v>
       </c>
       <c r="B16" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>131889562</v>
       </c>
       <c r="B17" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>131888310</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131888313</v>
       </c>
       <c r="B19" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>131889546</v>
       </c>
       <c r="B20" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>131889547</v>
       </c>
       <c r="B21" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888265</v>
+        <v>131888296</v>
       </c>
       <c r="B22" t="n">
-        <v>57907</v>
+        <v>91842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,29 +3233,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3265,10 +3264,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498010</v>
+        <v>498076</v>
       </c>
       <c r="R22" t="n">
-        <v>7040021</v>
+        <v>7040326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3305,7 +3304,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3314,6 +3313,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>131889564</v>
       </c>
       <c r="B23" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888296</v>
+        <v>131888265</v>
       </c>
       <c r="B24" t="n">
-        <v>91837</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,28 +3499,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3530,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498076</v>
+        <v>498010</v>
       </c>
       <c r="R24" t="n">
-        <v>7040326</v>
+        <v>7040021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3570,7 +3571,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3579,7 +3580,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>131888317</v>
       </c>
       <c r="B25" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>131888288</v>
       </c>
       <c r="B26" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>131888257</v>
       </c>
       <c r="B27" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>131889569</v>
       </c>
       <c r="B28" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131888269</v>
+        <v>131889558</v>
       </c>
       <c r="B29" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4157,29 +4157,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4189,10 +4184,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498161</v>
+        <v>498144</v>
       </c>
       <c r="R29" t="n">
-        <v>7040066</v>
+        <v>7040300</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4227,17 +4222,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4246,6 +4237,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4256,14 +4252,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4284,7 +4275,7 @@
         <v>131888263</v>
       </c>
       <c r="B30" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4411,10 +4402,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131889558</v>
+        <v>131888269</v>
       </c>
       <c r="B31" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4422,24 +4413,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4449,10 +4445,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498144</v>
+        <v>498161</v>
       </c>
       <c r="R31" t="n">
-        <v>7040300</v>
+        <v>7040066</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4487,13 +4483,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4502,11 +4502,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4517,9 +4512,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131888268</v>
+        <v>131889548</v>
       </c>
       <c r="B32" t="n">
-        <v>57907</v>
+        <v>91842</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,29 +4548,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4580,10 +4579,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498140</v>
+        <v>498083</v>
       </c>
       <c r="R32" t="n">
-        <v>7040032</v>
+        <v>7040302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4618,17 +4617,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4647,14 +4642,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4675,7 +4665,7 @@
         <v>131888318</v>
       </c>
       <c r="B33" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4801,7 +4791,7 @@
         <v>131888308</v>
       </c>
       <c r="B34" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4924,10 +4914,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131889548</v>
+        <v>131888268</v>
       </c>
       <c r="B35" t="n">
-        <v>91837</v>
+        <v>57912</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4935,28 +4925,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4966,10 +4957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498083</v>
+        <v>498140</v>
       </c>
       <c r="R35" t="n">
-        <v>7040302</v>
+        <v>7040032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5004,13 +4995,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5029,9 +5024,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131888261</v>
+        <v>131888287</v>
       </c>
       <c r="B36" t="n">
-        <v>57907</v>
+        <v>80379</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5060,29 +5060,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5092,10 +5091,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497929</v>
+        <v>498148</v>
       </c>
       <c r="R36" t="n">
-        <v>7040047</v>
+        <v>7040325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5132,7 +5131,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5141,6 +5140,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5151,22 +5151,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131888287</v>
+        <v>131889554</v>
       </c>
       <c r="B37" t="n">
-        <v>80374</v>
+        <v>91866</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5195,28 +5195,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5226,10 +5222,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>498148</v>
+        <v>498048</v>
       </c>
       <c r="R37" t="n">
-        <v>7040325</v>
+        <v>7040052</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5264,11 +5260,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5286,22 +5277,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5319,10 +5305,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131889554</v>
+        <v>131888261</v>
       </c>
       <c r="B38" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5330,24 +5316,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5357,10 +5348,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>498048</v>
+        <v>497929</v>
       </c>
       <c r="R38" t="n">
-        <v>7040052</v>
+        <v>7040047</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5395,13 +5386,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5420,9 +5415,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131888271</v>
+        <v>131889556</v>
       </c>
       <c r="B39" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5451,29 +5451,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>498306</v>
+        <v>498308</v>
       </c>
       <c r="R39" t="n">
-        <v>7040264</v>
+        <v>7040314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5521,17 +5516,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5550,14 +5541,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5575,10 +5561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131889556</v>
+        <v>131888271</v>
       </c>
       <c r="B40" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5586,24 +5572,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5613,10 +5604,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>498308</v>
+        <v>498306</v>
       </c>
       <c r="R40" t="n">
-        <v>7040314</v>
+        <v>7040264</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5651,13 +5642,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en grov stående död gran med 49 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5676,9 +5671,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
         <v>131888316</v>
       </c>
       <c r="B41" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5822,40 +5822,39 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888279</v>
+        <v>131888286</v>
       </c>
       <c r="B42" t="n">
-        <v>57095</v>
+        <v>80379</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5865,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498136</v>
+        <v>498252</v>
       </c>
       <c r="R42" t="n">
-        <v>7040344</v>
+        <v>7040210</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5905,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5914,12 +5913,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5937,10 +5957,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888286</v>
+        <v>131888295</v>
       </c>
       <c r="B43" t="n">
-        <v>80374</v>
+        <v>91842</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5948,28 +5968,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5979,10 +5999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498252</v>
+        <v>498147</v>
       </c>
       <c r="R43" t="n">
-        <v>7040210</v>
+        <v>7040335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6019,7 +6039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6039,22 +6059,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6072,39 +6092,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888295</v>
+        <v>131888279</v>
       </c>
       <c r="B44" t="n">
-        <v>91837</v>
+        <v>57100</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6114,10 +6135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498147</v>
+        <v>498136</v>
       </c>
       <c r="R44" t="n">
-        <v>7040335</v>
+        <v>7040344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6154,7 +6175,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6163,33 +6184,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
         <v>131888315</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>131888311</v>
       </c>
       <c r="B46" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131889541</v>
+        <v>131889803</v>
       </c>
       <c r="B47" t="n">
-        <v>78281</v>
+        <v>57912</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6475,26 +6475,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>498162</v>
+        <v>498061</v>
       </c>
       <c r="R47" t="n">
-        <v>7040231</v>
+        <v>7040333</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6540,13 +6545,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6557,7 +6566,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6570,9 +6579,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6593,7 +6607,7 @@
         <v>131889798</v>
       </c>
       <c r="B48" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6730,10 +6744,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889803</v>
+        <v>131889782</v>
       </c>
       <c r="B49" t="n">
-        <v>57907</v>
+        <v>91846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6741,29 +6755,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6773,10 +6786,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498061</v>
+        <v>498206</v>
       </c>
       <c r="R49" t="n">
-        <v>7040333</v>
+        <v>7040320</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6811,17 +6824,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6845,14 +6854,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6870,10 +6874,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131889782</v>
+        <v>131889541</v>
       </c>
       <c r="B50" t="n">
-        <v>91841</v>
+        <v>78286</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6881,30 +6885,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>498206</v>
+        <v>498162</v>
       </c>
       <c r="R50" t="n">
-        <v>7040320</v>
+        <v>7040231</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7000,10 +7000,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131889535</v>
+        <v>131889854</v>
       </c>
       <c r="B51" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7011,29 +7011,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7043,10 +7038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497945</v>
+        <v>498128</v>
       </c>
       <c r="R51" t="n">
-        <v>7040123</v>
+        <v>7040149</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7081,17 +7076,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7115,14 +7106,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7140,10 +7126,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889854</v>
+        <v>131889535</v>
       </c>
       <c r="B52" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7151,24 +7137,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7178,10 +7169,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>498128</v>
+        <v>497945</v>
       </c>
       <c r="R52" t="n">
-        <v>7040149</v>
+        <v>7040123</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7216,13 +7207,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7246,9 +7241,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
         <v>131889830</v>
       </c>
       <c r="B53" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>131889781</v>
       </c>
       <c r="B54" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131889826</v>
       </c>
       <c r="B55" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>131889822</v>
       </c>
       <c r="B56" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>131889824</v>
       </c>
       <c r="B57" t="n">
-        <v>83240</v>
+        <v>83245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>131889842</v>
       </c>
       <c r="B58" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>131889801</v>
       </c>
       <c r="B59" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>131889544</v>
       </c>
       <c r="B60" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>131889861</v>
       </c>
       <c r="B61" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>131889793</v>
       </c>
       <c r="B62" t="n">
-        <v>92564</v>
+        <v>92569</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>131889792</v>
       </c>
       <c r="B63" t="n">
-        <v>92564</v>
+        <v>92569</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8667,10 +8667,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889862</v>
+        <v>131889879</v>
       </c>
       <c r="B64" t="n">
-        <v>79269</v>
+        <v>89231</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8678,26 +8678,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8705,10 +8709,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>498155</v>
+        <v>498139</v>
       </c>
       <c r="R64" t="n">
-        <v>7040384</v>
+        <v>7040231</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8743,11 +8747,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8778,9 +8777,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8798,10 +8802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889879</v>
+        <v>131889862</v>
       </c>
       <c r="B65" t="n">
-        <v>89226</v>
+        <v>79274</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8809,30 +8813,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>498139</v>
+        <v>498155</v>
       </c>
       <c r="R65" t="n">
-        <v>7040231</v>
+        <v>7040384</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8878,6 +8878,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8908,14 +8913,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8936,7 +8936,7 @@
         <v>131889780</v>
       </c>
       <c r="B66" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889537</v>
+        <v>131889846</v>
       </c>
       <c r="B67" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,29 +9074,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498206</v>
+        <v>498217</v>
       </c>
       <c r="R67" t="n">
-        <v>7040254</v>
+        <v>7040214</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9144,17 +9139,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9163,11 +9154,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9178,14 +9164,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9203,10 +9184,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889846</v>
+        <v>131889537</v>
       </c>
       <c r="B68" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9214,24 +9195,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9241,10 +9227,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498217</v>
+        <v>498206</v>
       </c>
       <c r="R68" t="n">
-        <v>7040214</v>
+        <v>7040254</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9279,13 +9265,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9294,6 +9284,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ68" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9304,9 +9299,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9327,7 +9327,7 @@
         <v>131889858</v>
       </c>
       <c r="B69" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>131889837</v>
       </c>
       <c r="B70" t="n">
-        <v>91855</v>
+        <v>91860</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9593,37 +9593,41 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889860</v>
+        <v>131889794</v>
       </c>
       <c r="B71" t="n">
-        <v>79269</v>
+        <v>92569</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9631,10 +9635,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498192</v>
+        <v>498247</v>
       </c>
       <c r="R71" t="n">
-        <v>7040190</v>
+        <v>7040357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9669,11 +9673,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9686,7 +9685,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9722,7 +9726,7 @@
         <v>131889538</v>
       </c>
       <c r="B72" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,10 +9853,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889536</v>
+        <v>131889860</v>
       </c>
       <c r="B73" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9860,31 +9864,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9892,10 +9891,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498140</v>
+        <v>498192</v>
       </c>
       <c r="R73" t="n">
-        <v>7040150</v>
+        <v>7040190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9932,7 +9931,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9941,17 +9940,13 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9984,39 +9979,40 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889794</v>
+        <v>131889536</v>
       </c>
       <c r="B74" t="n">
-        <v>92564</v>
+        <v>57912</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10026,10 +10022,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498247</v>
+        <v>498140</v>
       </c>
       <c r="R74" t="n">
-        <v>7040357</v>
+        <v>7040150</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10064,19 +10060,23 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
@@ -10117,7 +10117,7 @@
         <v>131889843</v>
       </c>
       <c r="B75" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>131889799</v>
       </c>
       <c r="B76" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10375,40 +10375,39 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889800</v>
+        <v>131889841</v>
       </c>
       <c r="B77" t="n">
-        <v>57907</v>
+        <v>92220</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10418,10 +10417,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498089</v>
+        <v>498085</v>
       </c>
       <c r="R77" t="n">
-        <v>7040360</v>
+        <v>7040081</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10456,17 +10455,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10482,22 +10477,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10518,7 +10513,7 @@
         <v>131889825</v>
       </c>
       <c r="B78" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10648,7 +10643,7 @@
         <v>131889833</v>
       </c>
       <c r="B79" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10778,7 +10773,7 @@
         <v>131889788</v>
       </c>
       <c r="B80" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10905,39 +10900,40 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131889841</v>
+        <v>131889800</v>
       </c>
       <c r="B81" t="n">
-        <v>92215</v>
+        <v>57912</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10947,10 +10943,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498085</v>
+        <v>498089</v>
       </c>
       <c r="R81" t="n">
-        <v>7040081</v>
+        <v>7040360</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10985,13 +10981,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11007,22 +11007,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11043,7 +11043,7 @@
         <v>131889787</v>
       </c>
       <c r="B82" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>131889857</v>
       </c>
       <c r="B83" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>131889844</v>
       </c>
       <c r="B84" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11427,37 +11427,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889845</v>
+        <v>131889539</v>
       </c>
       <c r="B85" t="n">
-        <v>91861</v>
+        <v>83245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>498096</v>
+        <v>498080</v>
       </c>
       <c r="R85" t="n">
-        <v>7040105</v>
+        <v>7040050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11520,22 +11520,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Naturskog med påtagligt höga naturvärden.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11553,37 +11538,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889539</v>
+        <v>131889845</v>
       </c>
       <c r="B86" t="n">
-        <v>83240</v>
+        <v>91866</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11591,10 +11576,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498080</v>
+        <v>498096</v>
       </c>
       <c r="R86" t="n">
-        <v>7040050</v>
+        <v>7040105</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11646,7 +11631,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Naturskog med påtagligt höga naturvärden.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11667,7 +11667,7 @@
         <v>131889779</v>
       </c>
       <c r="B87" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>131889529</v>
       </c>
       <c r="B88" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>131889877</v>
       </c>
       <c r="B89" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131888264</v>
+        <v>131888312</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,31 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497993</v>
+        <v>498192</v>
       </c>
       <c r="R3" t="n">
-        <v>7040023</v>
+        <v>7040124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +859,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,12 +889,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131888312</v>
+        <v>131888264</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,26 +923,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498192</v>
+        <v>497993</v>
       </c>
       <c r="R4" t="n">
-        <v>7040124</v>
+        <v>7040023</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Ringhack, äldre, på en gran vid kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1004,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131889553</v>
+        <v>131888294</v>
       </c>
       <c r="B12" t="n">
-        <v>91866</v>
+        <v>91842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,19 +1933,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -1960,10 +1964,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497949</v>
+        <v>498217</v>
       </c>
       <c r="R12" t="n">
-        <v>7040132</v>
+        <v>7040172</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1998,6 +2002,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2023,9 +2032,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2043,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888294</v>
+        <v>131889553</v>
       </c>
       <c r="B13" t="n">
-        <v>91842</v>
+        <v>91866</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,23 +2068,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -2085,10 +2095,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498217</v>
+        <v>497949</v>
       </c>
       <c r="R13" t="n">
-        <v>7040172</v>
+        <v>7040132</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,11 +2133,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2153,14 +2158,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888296</v>
+        <v>131888265</v>
       </c>
       <c r="B22" t="n">
-        <v>91842</v>
+        <v>57912</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,28 +3233,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3264,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498076</v>
+        <v>498010</v>
       </c>
       <c r="R22" t="n">
-        <v>7040326</v>
+        <v>7040021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3304,7 +3305,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,7 +3314,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131889564</v>
+        <v>131888296</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>91842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,26 +3363,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3390,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498048</v>
+        <v>498076</v>
       </c>
       <c r="R23" t="n">
-        <v>7040043</v>
+        <v>7040326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3430,7 +3434,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3448,11 +3452,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3463,14 +3462,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3488,10 +3482,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888265</v>
+        <v>131889564</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3499,31 +3493,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3531,10 +3520,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498010</v>
+        <v>498048</v>
       </c>
       <c r="R24" t="n">
-        <v>7040021</v>
+        <v>7040043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3571,7 +3560,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3580,6 +3569,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3588,6 +3578,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3598,9 +3593,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131889548</v>
+        <v>131888318</v>
       </c>
       <c r="B32" t="n">
-        <v>91842</v>
+        <v>79274</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,30 +4548,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4579,10 +4575,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498083</v>
+        <v>498079</v>
       </c>
       <c r="R32" t="n">
-        <v>7040302</v>
+        <v>7040353</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4615,6 +4611,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4662,7 +4663,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888318</v>
+        <v>131888308</v>
       </c>
       <c r="B33" t="n">
         <v>79274</v>
@@ -4700,10 +4701,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498079</v>
+        <v>497942</v>
       </c>
       <c r="R33" t="n">
-        <v>7040353</v>
+        <v>7040052</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4740,7 +4741,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4788,10 +4789,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888308</v>
+        <v>131889548</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>91842</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4799,26 +4800,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4826,10 +4831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497942</v>
+        <v>498083</v>
       </c>
       <c r="R34" t="n">
-        <v>7040052</v>
+        <v>7040302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4862,11 +4867,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5184,10 +5184,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131889554</v>
+        <v>131888261</v>
       </c>
       <c r="B37" t="n">
-        <v>91866</v>
+        <v>57912</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5195,24 +5195,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5222,10 +5227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>498048</v>
+        <v>497929</v>
       </c>
       <c r="R37" t="n">
-        <v>7040052</v>
+        <v>7040047</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5260,13 +5265,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5285,9 +5294,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5305,10 +5319,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131888261</v>
+        <v>131889554</v>
       </c>
       <c r="B38" t="n">
-        <v>57912</v>
+        <v>91866</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5316,29 +5330,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5348,10 +5357,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497929</v>
+        <v>498048</v>
       </c>
       <c r="R38" t="n">
-        <v>7040047</v>
+        <v>7040052</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5386,17 +5395,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5415,14 +5420,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889801</v>
+        <v>131889544</v>
       </c>
       <c r="B59" t="n">
-        <v>57912</v>
+        <v>78286</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8016,31 +8016,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8048,10 +8043,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498071</v>
+        <v>498103</v>
       </c>
       <c r="R59" t="n">
-        <v>7040353</v>
+        <v>7040280</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8086,17 +8081,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8107,7 +8098,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8120,14 +8111,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8145,10 +8131,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889544</v>
+        <v>131889801</v>
       </c>
       <c r="B60" t="n">
-        <v>78286</v>
+        <v>57912</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8156,26 +8142,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8183,10 +8174,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498103</v>
+        <v>498071</v>
       </c>
       <c r="R60" t="n">
-        <v>7040280</v>
+        <v>7040353</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8221,13 +8212,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8238,7 +8233,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8251,9 +8246,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -11427,37 +11427,41 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889539</v>
+        <v>131889779</v>
       </c>
       <c r="B85" t="n">
-        <v>83245</v>
+        <v>91846</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11465,10 +11469,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>498080</v>
+        <v>498070</v>
       </c>
       <c r="R85" t="n">
-        <v>7040050</v>
+        <v>7040031</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11520,7 +11524,27 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Naturskog med påtagligt höga naturvärden.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11538,10 +11562,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889845</v>
+        <v>131889529</v>
       </c>
       <c r="B86" t="n">
-        <v>91866</v>
+        <v>91846</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11549,19 +11573,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -11576,10 +11604,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498096</v>
+        <v>498137</v>
       </c>
       <c r="R86" t="n">
-        <v>7040105</v>
+        <v>7040255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11664,41 +11692,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889779</v>
+        <v>131889539</v>
       </c>
       <c r="B87" t="n">
-        <v>91846</v>
+        <v>83245</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11706,10 +11730,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>498070</v>
+        <v>498080</v>
       </c>
       <c r="R87" t="n">
-        <v>7040031</v>
+        <v>7040050</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11761,27 +11785,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Naturskog med påtagligt höga naturvärden.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11799,10 +11803,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889529</v>
+        <v>131889845</v>
       </c>
       <c r="B88" t="n">
-        <v>91846</v>
+        <v>91866</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11810,23 +11814,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>498137</v>
+        <v>498096</v>
       </c>
       <c r="R88" t="n">
-        <v>7040255</v>
+        <v>7040105</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 17217-2021 artfynd.xlsx
+++ b/artfynd/A 17217-2021 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>131888312</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>131888264</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,38 +1047,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888283</v>
+        <v>131888266</v>
       </c>
       <c r="B5" t="n">
-        <v>97917</v>
+        <v>57914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498177</v>
+        <v>498035</v>
       </c>
       <c r="R5" t="n">
-        <v>7040311</v>
+        <v>7040010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,19 +1128,38 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,7 +1180,7 @@
         <v>131888314</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,42 +1303,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888266</v>
+        <v>131888283</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>97919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,10 +1342,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498035</v>
+        <v>498177</v>
       </c>
       <c r="R7" t="n">
-        <v>7040010</v>
+        <v>7040311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,38 +1380,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>131889570</v>
       </c>
       <c r="B8" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>131888258</v>
       </c>
       <c r="B9" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>131889555</v>
       </c>
       <c r="B10" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>131888262</v>
       </c>
       <c r="B11" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888294</v>
+        <v>131889553</v>
       </c>
       <c r="B12" t="n">
-        <v>91842</v>
+        <v>91868</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,23 +1933,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -1964,10 +1960,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498217</v>
+        <v>497949</v>
       </c>
       <c r="R12" t="n">
-        <v>7040172</v>
+        <v>7040132</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2002,11 +1998,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2032,14 +2023,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,10 +2043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131889553</v>
+        <v>131888294</v>
       </c>
       <c r="B13" t="n">
-        <v>91866</v>
+        <v>91844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,19 +2054,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -2095,10 +2085,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497949</v>
+        <v>498217</v>
       </c>
       <c r="R13" t="n">
-        <v>7040132</v>
+        <v>7040172</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2133,6 +2123,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2158,9 +2153,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
         <v>131888272</v>
       </c>
       <c r="B14" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131888270</v>
       </c>
       <c r="B15" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>131888309</v>
       </c>
       <c r="B16" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>131889562</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>131888310</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131888313</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>131889546</v>
       </c>
       <c r="B20" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>131889547</v>
       </c>
       <c r="B21" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131888265</v>
+        <v>131888296</v>
       </c>
       <c r="B22" t="n">
-        <v>57912</v>
+        <v>91844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,29 +3233,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3265,10 +3264,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498010</v>
+        <v>498076</v>
       </c>
       <c r="R22" t="n">
-        <v>7040021</v>
+        <v>7040326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3305,7 +3304,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3314,6 +3313,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131888296</v>
+        <v>131889564</v>
       </c>
       <c r="B23" t="n">
-        <v>91842</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,30 +3363,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3394,10 +3390,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498076</v>
+        <v>498048</v>
       </c>
       <c r="R23" t="n">
-        <v>7040326</v>
+        <v>7040043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3434,7 +3430,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3452,6 +3448,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3462,9 +3463,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3482,10 +3488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131889564</v>
+        <v>131888265</v>
       </c>
       <c r="B24" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3493,26 +3499,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3520,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498048</v>
+        <v>498010</v>
       </c>
       <c r="R24" t="n">
-        <v>7040043</v>
+        <v>7040021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3560,7 +3571,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3569,7 +3580,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3578,11 +3588,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3593,14 +3598,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
         <v>131888317</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>131888288</v>
       </c>
       <c r="B26" t="n">
-        <v>80415</v>
+        <v>80417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888257</v>
+        <v>131889569</v>
       </c>
       <c r="B27" t="n">
-        <v>83254</v>
+        <v>83122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498300</v>
+        <v>498205</v>
       </c>
       <c r="R27" t="n">
-        <v>7040266</v>
+        <v>7040233</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3960,11 +3960,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På barken av en stående grov gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3995,14 +3990,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4020,10 +4010,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131889569</v>
+        <v>131888257</v>
       </c>
       <c r="B28" t="n">
-        <v>83120</v>
+        <v>83256</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4031,21 +4021,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4058,10 +4048,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498205</v>
+        <v>498300</v>
       </c>
       <c r="R28" t="n">
-        <v>7040233</v>
+        <v>7040266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4096,6 +4086,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På barken av en stående grov gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4126,9 +4121,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
         <v>131889558</v>
       </c>
       <c r="B29" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>131888263</v>
       </c>
       <c r="B30" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>131888269</v>
       </c>
       <c r="B31" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131888318</v>
+        <v>131889548</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>91844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4548,26 +4548,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4575,10 +4579,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498079</v>
+        <v>498083</v>
       </c>
       <c r="R32" t="n">
-        <v>7040353</v>
+        <v>7040302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4611,11 +4615,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4663,10 +4662,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888308</v>
+        <v>131888318</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4701,10 +4700,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497942</v>
+        <v>498079</v>
       </c>
       <c r="R33" t="n">
-        <v>7040052</v>
+        <v>7040353</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4741,7 +4740,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4789,10 +4788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131889548</v>
+        <v>131888308</v>
       </c>
       <c r="B34" t="n">
-        <v>91842</v>
+        <v>79276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4800,30 +4799,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498083</v>
+        <v>497942</v>
       </c>
       <c r="R34" t="n">
-        <v>7040302</v>
+        <v>7040052</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4867,6 +4862,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4917,7 +4917,7 @@
         <v>131888268</v>
       </c>
       <c r="B35" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131888287</v>
+        <v>131888261</v>
       </c>
       <c r="B36" t="n">
-        <v>80379</v>
+        <v>57914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5060,28 +5060,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5091,10 +5092,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>498148</v>
+        <v>497929</v>
       </c>
       <c r="R36" t="n">
-        <v>7040325</v>
+        <v>7040047</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5131,7 +5132,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5140,7 +5141,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5151,22 +5151,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131888261</v>
+        <v>131888287</v>
       </c>
       <c r="B37" t="n">
-        <v>57912</v>
+        <v>80381</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5195,29 +5195,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5227,10 +5226,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497929</v>
+        <v>498148</v>
       </c>
       <c r="R37" t="n">
-        <v>7040047</v>
+        <v>7040325</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5267,7 +5266,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, glest spridda längs några meter på en gran.</t>
+          <t>På en björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5276,6 +5275,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5286,22 +5286,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
         <v>131889554</v>
       </c>
       <c r="B38" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>131889556</v>
       </c>
       <c r="B39" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>131888271</v>
       </c>
       <c r="B40" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>131888316</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888286</v>
+        <v>131888295</v>
       </c>
       <c r="B42" t="n">
-        <v>80379</v>
+        <v>91844</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498252</v>
+        <v>498147</v>
       </c>
       <c r="R42" t="n">
-        <v>7040210</v>
+        <v>7040335</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på en grovbarkad gammal sälg.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888295</v>
+        <v>131888286</v>
       </c>
       <c r="B43" t="n">
-        <v>91842</v>
+        <v>80381</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5968,28 +5968,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498147</v>
+        <v>498252</v>
       </c>
       <c r="R43" t="n">
-        <v>7040335</v>
+        <v>7040210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Rikligt på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
         <v>131888279</v>
       </c>
       <c r="B44" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>131888315</v>
       </c>
       <c r="B45" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>131888311</v>
       </c>
       <c r="B46" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131889803</v>
+        <v>131889782</v>
       </c>
       <c r="B47" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6475,29 +6475,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6507,10 +6506,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>498061</v>
+        <v>498206</v>
       </c>
       <c r="R47" t="n">
-        <v>7040333</v>
+        <v>7040320</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6545,17 +6544,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6579,14 +6574,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6604,10 +6594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131889798</v>
+        <v>131889803</v>
       </c>
       <c r="B48" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6647,10 +6637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>498109</v>
+        <v>498061</v>
       </c>
       <c r="R48" t="n">
-        <v>7040366</v>
+        <v>7040333</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,10 +6734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131889782</v>
+        <v>131889798</v>
       </c>
       <c r="B49" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6755,28 +6745,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6786,10 +6777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>498206</v>
+        <v>498109</v>
       </c>
       <c r="R49" t="n">
-        <v>7040320</v>
+        <v>7040366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6824,13 +6815,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6854,9 +6849,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6877,7 +6877,7 @@
         <v>131889541</v>
       </c>
       <c r="B50" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>131889854</v>
       </c>
       <c r="B51" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>131889535</v>
       </c>
       <c r="B52" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889830</v>
+        <v>131889781</v>
       </c>
       <c r="B53" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7277,21 +7277,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>498191</v>
+        <v>498266</v>
       </c>
       <c r="R53" t="n">
-        <v>7040363</v>
+        <v>7040341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7359,6 +7359,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7376,10 +7396,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889781</v>
+        <v>131889830</v>
       </c>
       <c r="B54" t="n">
-        <v>91846</v>
+        <v>91844</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7387,21 +7407,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7418,10 +7438,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>498266</v>
+        <v>498191</v>
       </c>
       <c r="R54" t="n">
-        <v>7040341</v>
+        <v>7040363</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7469,26 +7489,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7509,7 +7509,7 @@
         <v>131889826</v>
       </c>
       <c r="B55" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>131889822</v>
       </c>
       <c r="B56" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>131889824</v>
       </c>
       <c r="B57" t="n">
-        <v>83245</v>
+        <v>83247</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>131889842</v>
       </c>
       <c r="B58" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889544</v>
+        <v>131889801</v>
       </c>
       <c r="B59" t="n">
-        <v>78286</v>
+        <v>57914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8016,26 +8016,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8043,10 +8048,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498103</v>
+        <v>498071</v>
       </c>
       <c r="R59" t="n">
-        <v>7040280</v>
+        <v>7040353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8081,13 +8086,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8098,7 +8107,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8111,9 +8120,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8131,10 +8145,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889801</v>
+        <v>131889544</v>
       </c>
       <c r="B60" t="n">
-        <v>57912</v>
+        <v>78288</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8142,31 +8156,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8174,10 +8183,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498071</v>
+        <v>498103</v>
       </c>
       <c r="R60" t="n">
-        <v>7040353</v>
+        <v>7040280</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8212,17 +8221,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8233,7 +8238,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8246,14 +8251,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8274,7 +8274,7 @@
         <v>131889861</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>131889793</v>
       </c>
       <c r="B62" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>131889792</v>
       </c>
       <c r="B63" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>131889879</v>
       </c>
       <c r="B64" t="n">
-        <v>89231</v>
+        <v>89233</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>131889862</v>
       </c>
       <c r="B65" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>131889780</v>
       </c>
       <c r="B66" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889846</v>
+        <v>131889858</v>
       </c>
       <c r="B67" t="n">
-        <v>91866</v>
+        <v>79276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9074,26 +9074,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9101,10 +9109,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498217</v>
+        <v>498181</v>
       </c>
       <c r="R67" t="n">
-        <v>7040214</v>
+        <v>7040135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9139,6 +9147,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Särskilt rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9151,7 +9164,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9164,9 +9177,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9184,10 +9202,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889537</v>
+        <v>131889846</v>
       </c>
       <c r="B68" t="n">
-        <v>57912</v>
+        <v>91868</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9195,29 +9213,24 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9227,10 +9240,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498206</v>
+        <v>498217</v>
       </c>
       <c r="R68" t="n">
-        <v>7040254</v>
+        <v>7040214</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9265,17 +9278,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9284,11 +9293,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ68" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9299,14 +9303,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9324,10 +9323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889858</v>
+        <v>131889537</v>
       </c>
       <c r="B69" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9335,34 +9334,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9370,10 +9366,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498181</v>
+        <v>498206</v>
       </c>
       <c r="R69" t="n">
-        <v>7040135</v>
+        <v>7040254</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9410,7 +9406,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Särskilt rikligt med garnlav här!</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9419,13 +9415,17 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
         <v>131889837</v>
       </c>
       <c r="B70" t="n">
-        <v>91860</v>
+        <v>91862</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9593,41 +9593,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889794</v>
+        <v>131889860</v>
       </c>
       <c r="B71" t="n">
-        <v>92569</v>
+        <v>79276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9635,10 +9631,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498247</v>
+        <v>498192</v>
       </c>
       <c r="R71" t="n">
-        <v>7040357</v>
+        <v>7040190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9673,6 +9669,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9685,12 +9686,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9723,40 +9719,39 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889538</v>
+        <v>131889794</v>
       </c>
       <c r="B72" t="n">
-        <v>57909</v>
+        <v>92571</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9766,10 +9761,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>498308</v>
+        <v>498247</v>
       </c>
       <c r="R72" t="n">
-        <v>7040314</v>
+        <v>7040357</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9804,23 +9799,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9853,10 +9849,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889860</v>
+        <v>131889536</v>
       </c>
       <c r="B73" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9864,26 +9860,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9891,10 +9892,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498192</v>
+        <v>498140</v>
       </c>
       <c r="R73" t="n">
-        <v>7040190</v>
+        <v>7040150</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9931,7 +9932,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9940,13 +9941,17 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9979,10 +9984,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889536</v>
+        <v>131889538</v>
       </c>
       <c r="B74" t="n">
-        <v>57912</v>
+        <v>57911</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9990,16 +9995,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10012,7 +10017,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10022,10 +10027,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498140</v>
+        <v>498308</v>
       </c>
       <c r="R74" t="n">
-        <v>7040150</v>
+        <v>7040314</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10062,7 +10067,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10077,11 +10082,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10117,7 +10117,7 @@
         <v>131889843</v>
       </c>
       <c r="B75" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>131889799</v>
       </c>
       <c r="B76" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10375,39 +10375,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889841</v>
+        <v>131889800</v>
       </c>
       <c r="B77" t="n">
-        <v>92220</v>
+        <v>57914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10417,10 +10418,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498085</v>
+        <v>498089</v>
       </c>
       <c r="R77" t="n">
-        <v>7040081</v>
+        <v>7040360</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10455,13 +10456,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10477,22 +10482,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10510,32 +10515,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889825</v>
+        <v>131889833</v>
       </c>
       <c r="B78" t="n">
-        <v>92306</v>
+        <v>91844</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10552,10 +10557,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498076</v>
+        <v>498237</v>
       </c>
       <c r="R78" t="n">
-        <v>7040226</v>
+        <v>7040342</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10640,32 +10645,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889833</v>
+        <v>131889825</v>
       </c>
       <c r="B79" t="n">
-        <v>91842</v>
+        <v>92308</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10682,10 +10687,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>498237</v>
+        <v>498076</v>
       </c>
       <c r="R79" t="n">
-        <v>7040342</v>
+        <v>7040226</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10773,7 +10778,7 @@
         <v>131889788</v>
       </c>
       <c r="B80" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10900,40 +10905,39 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131889800</v>
+        <v>131889841</v>
       </c>
       <c r="B81" t="n">
-        <v>57912</v>
+        <v>92222</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10943,10 +10947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498089</v>
+        <v>498085</v>
       </c>
       <c r="R81" t="n">
-        <v>7040360</v>
+        <v>7040081</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10981,17 +10985,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11007,22 +11007,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11043,7 +11043,7 @@
         <v>131889787</v>
       </c>
       <c r="B82" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>131889857</v>
       </c>
       <c r="B83" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>131889844</v>
       </c>
       <c r="B84" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11427,41 +11427,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889779</v>
+        <v>131889539</v>
       </c>
       <c r="B85" t="n">
-        <v>91846</v>
+        <v>83247</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11469,10 +11465,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>498070</v>
+        <v>498080</v>
       </c>
       <c r="R85" t="n">
-        <v>7040031</v>
+        <v>7040050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11524,27 +11520,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Naturskog med påtagligt höga naturvärden.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11562,10 +11538,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889529</v>
+        <v>131889779</v>
       </c>
       <c r="B86" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11604,10 +11580,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498137</v>
+        <v>498070</v>
       </c>
       <c r="R86" t="n">
-        <v>7040255</v>
+        <v>7040031</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11672,9 +11648,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11692,37 +11673,41 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889539</v>
+        <v>131889529</v>
       </c>
       <c r="B87" t="n">
-        <v>83245</v>
+        <v>91848</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11730,10 +11715,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>498080</v>
+        <v>498137</v>
       </c>
       <c r="R87" t="n">
-        <v>7040050</v>
+        <v>7040255</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11785,7 +11770,22 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Naturskog med påtagligt höga naturvärden.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
         <v>131889845</v>
       </c>
       <c r="B88" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>131889877</v>
       </c>
       <c r="B89" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
